--- a/python-service/pan_issue_rows_debug.xlsx
+++ b/python-service/pan_issue_rows_debug.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="532">
   <si>
     <t>rowNumber</t>
   </si>
@@ -49,229 +49,1567 @@
     <t>messages</t>
   </si>
   <si>
+    <t>09-04-2025</t>
+  </si>
+  <si>
+    <t>27-04-2025</t>
+  </si>
+  <si>
+    <t>22-04-2025</t>
+  </si>
+  <si>
+    <t>04-04-2025</t>
+  </si>
+  <si>
+    <t>26-04-2025</t>
+  </si>
+  <si>
+    <t>12-04-2025</t>
+  </si>
+  <si>
+    <t>24-04-2025</t>
+  </si>
+  <si>
+    <t>16-04-2025</t>
+  </si>
+  <si>
     <t>02-04-2025</t>
   </si>
   <si>
+    <t>10-04-2025</t>
+  </si>
+  <si>
+    <t>28-04-2025</t>
+  </si>
+  <si>
+    <t>11-04-2025</t>
+  </si>
+  <si>
+    <t>05-04-2025</t>
+  </si>
+  <si>
+    <t>07-04-2025</t>
+  </si>
+  <si>
+    <t>21-04-2025</t>
+  </si>
+  <si>
+    <t>08-04-2025</t>
+  </si>
+  <si>
+    <t>19-04-2025</t>
+  </si>
+  <si>
+    <t>15-04-2025</t>
+  </si>
+  <si>
+    <t>01-04-2025</t>
+  </si>
+  <si>
+    <t>18-04-2025</t>
+  </si>
+  <si>
+    <t>06-04-2025</t>
+  </si>
+  <si>
+    <t>23-04-2025</t>
+  </si>
+  <si>
+    <t>29-04-2025</t>
+  </si>
+  <si>
+    <t>13-04-2025</t>
+  </si>
+  <si>
+    <t>14-04-2025</t>
+  </si>
+  <si>
+    <t>30-04-2025</t>
+  </si>
+  <si>
+    <t>17-04-2025</t>
+  </si>
+  <si>
+    <t>20-04-2025</t>
+  </si>
+  <si>
+    <t>25-04-2025</t>
+  </si>
+  <si>
     <t>03-04-2025</t>
   </si>
   <si>
-    <t>05-04-2025</t>
-  </si>
-  <si>
-    <t>09-04-2025</t>
-  </si>
-  <si>
-    <t>10-04-2025</t>
-  </si>
-  <si>
-    <t>15-04-2025</t>
-  </si>
-  <si>
-    <t>17-04-2025</t>
-  </si>
-  <si>
-    <t>18-04-2025</t>
-  </si>
-  <si>
-    <t>21-04-2025</t>
-  </si>
-  <si>
-    <t>25-04-2025</t>
-  </si>
-  <si>
-    <t>27-04-2025</t>
-  </si>
-  <si>
-    <t>28-04-2025</t>
-  </si>
-  <si>
-    <t>29-04-2025</t>
-  </si>
-  <si>
-    <t>JH/2526/ 15</t>
-  </si>
-  <si>
-    <t>JH/2526/ 18</t>
-  </si>
-  <si>
-    <t>JH/2526/ 66</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 1</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 2</t>
-  </si>
-  <si>
-    <t>JH/2526/ 120</t>
-  </si>
-  <si>
-    <t>JH/2526/ 275</t>
-  </si>
-  <si>
-    <t>JH/2526/ 278</t>
-  </si>
-  <si>
-    <t>JH/2526/ 321</t>
-  </si>
-  <si>
-    <t>JH/2526/ 329</t>
-  </si>
-  <si>
-    <t>JH/2526/ 480</t>
-  </si>
-  <si>
-    <t>JH/2526/ 645</t>
-  </si>
-  <si>
-    <t>JH/2526/ 681</t>
-  </si>
-  <si>
-    <t>JH/2526/ 683</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 3</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 4</t>
-  </si>
-  <si>
-    <t>JH/2526/ 910</t>
-  </si>
-  <si>
-    <t>JH/2526/ 939</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 5</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 7</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 8</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 9</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 13</t>
-  </si>
-  <si>
-    <t>JH/B/2526/ 14</t>
-  </si>
-  <si>
-    <t>Mrs. Tanuja Vemuri Bandi</t>
-  </si>
-  <si>
-    <t>Mrs. Revathi Krushi Duggirala</t>
-  </si>
-  <si>
-    <t>Mrs. Srilakshmi Veeramachineni</t>
-  </si>
-  <si>
-    <t>Kundan Crafts Private Limited</t>
-  </si>
-  <si>
-    <t>House of B N M Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Ram Sunder R Kadari</t>
-  </si>
-  <si>
-    <t>Mrs. Krishna Varshitha Kotha,</t>
-  </si>
-  <si>
-    <t>Mrs. Varija Koppu,</t>
-  </si>
-  <si>
-    <t>Mrs. Sarvani Manne,</t>
-  </si>
-  <si>
-    <t>Mrs. Renuka Rao Joopelli,</t>
-  </si>
-  <si>
-    <t>Mrs. Lavanya Gajjala</t>
-  </si>
-  <si>
-    <t>Mrs. Srujana Alle,</t>
-  </si>
-  <si>
-    <t>Mr. Srinivasa Rao Myneni,</t>
-  </si>
-  <si>
-    <t>Mrs. Kavitha Guduru</t>
-  </si>
-  <si>
-    <t>Mrs. Aagya Mathur,</t>
-  </si>
-  <si>
-    <t>Guru Kripa Design Studio Private Limited - MSME Small</t>
-  </si>
-  <si>
-    <t>S K Seth Jewellers</t>
-  </si>
-  <si>
-    <t>AAECK7089G</t>
-  </si>
-  <si>
-    <t>AAGCH4557C</t>
-  </si>
-  <si>
-    <t>AAJCG9820E</t>
-  </si>
-  <si>
-    <t>AACFS2877H</t>
-  </si>
-  <si>
-    <t>US DL No. 29343335</t>
-  </si>
-  <si>
-    <t>USDL No: 25285694</t>
-  </si>
-  <si>
-    <t>US DL NO. A60887866</t>
-  </si>
-  <si>
-    <t>US DL NO. K36073669224</t>
-  </si>
-  <si>
-    <t>US DL NO. 46741808</t>
-  </si>
-  <si>
-    <t>USDL No: S64616170</t>
-  </si>
-  <si>
-    <t>USDL - S30740174</t>
-  </si>
-  <si>
-    <t>US DL NO. 14383883</t>
-  </si>
-  <si>
-    <t>AUS DL NO. 042561333</t>
-  </si>
-  <si>
-    <t>US DL NO. 948265618</t>
-  </si>
-  <si>
-    <t>DL No. 46474713</t>
-  </si>
-  <si>
-    <t>US DL NO. B65370662</t>
-  </si>
-  <si>
-    <t>USDL No: T61786432</t>
+    <t>JH/25-26 17</t>
+  </si>
+  <si>
+    <t>JH/25-26 31</t>
+  </si>
+  <si>
+    <t>JH/25-26 51</t>
+  </si>
+  <si>
+    <t>JH/25-26 54</t>
+  </si>
+  <si>
+    <t>JH/25-26 57</t>
+  </si>
+  <si>
+    <t>JH/25-26 67</t>
+  </si>
+  <si>
+    <t>JH/25-26 73</t>
+  </si>
+  <si>
+    <t>JH/25-26 79</t>
+  </si>
+  <si>
+    <t>JH/25-26 94</t>
+  </si>
+  <si>
+    <t>JH/25-26 108</t>
+  </si>
+  <si>
+    <t>JH/25-26 109</t>
+  </si>
+  <si>
+    <t>JH/25-26 119</t>
+  </si>
+  <si>
+    <t>JH/25-26 126</t>
+  </si>
+  <si>
+    <t>JH/25-26 127</t>
+  </si>
+  <si>
+    <t>JH/25-26 157</t>
+  </si>
+  <si>
+    <t>JH/25-26 162</t>
+  </si>
+  <si>
+    <t>JH/25-26 164</t>
+  </si>
+  <si>
+    <t>JH/25-26 185</t>
+  </si>
+  <si>
+    <t>JH/25-26 186</t>
+  </si>
+  <si>
+    <t>JH/25-26 188</t>
+  </si>
+  <si>
+    <t>JH/25-26 227</t>
+  </si>
+  <si>
+    <t>JH/25-26 233</t>
+  </si>
+  <si>
+    <t>JH/25-26 252</t>
+  </si>
+  <si>
+    <t>JH/25-26 273</t>
+  </si>
+  <si>
+    <t>JH/25-26 295</t>
+  </si>
+  <si>
+    <t>JH/25-26 296</t>
+  </si>
+  <si>
+    <t>JH/25-26 300</t>
+  </si>
+  <si>
+    <t>JH/25-26 311</t>
+  </si>
+  <si>
+    <t>JH/25-26 316</t>
+  </si>
+  <si>
+    <t>JH/25-26 321</t>
+  </si>
+  <si>
+    <t>JH/25-26 327</t>
+  </si>
+  <si>
+    <t>JH/25-26 329</t>
+  </si>
+  <si>
+    <t>JH/25-26 330</t>
+  </si>
+  <si>
+    <t>JH/25-26 346</t>
+  </si>
+  <si>
+    <t>JH/25-26 349</t>
+  </si>
+  <si>
+    <t>JH/25-26 351</t>
+  </si>
+  <si>
+    <t>JH/25-26 353</t>
+  </si>
+  <si>
+    <t>JH/25-26 356</t>
+  </si>
+  <si>
+    <t>JH/25-26 364</t>
+  </si>
+  <si>
+    <t>JH/25-26 370</t>
+  </si>
+  <si>
+    <t>JH/25-26 376</t>
+  </si>
+  <si>
+    <t>JH/25-26 378</t>
+  </si>
+  <si>
+    <t>JH/25-26 380</t>
+  </si>
+  <si>
+    <t>JH/25-26 396</t>
+  </si>
+  <si>
+    <t>JH/25-26 397</t>
+  </si>
+  <si>
+    <t>JH/25-26 416</t>
+  </si>
+  <si>
+    <t>JH/25-26 426</t>
+  </si>
+  <si>
+    <t>JH/25-26 441</t>
+  </si>
+  <si>
+    <t>JH/25-26 447</t>
+  </si>
+  <si>
+    <t>JH/25-26 452</t>
+  </si>
+  <si>
+    <t>JH/25-26 462</t>
+  </si>
+  <si>
+    <t>JH/25-26 484</t>
+  </si>
+  <si>
+    <t>JH/25-26 498</t>
+  </si>
+  <si>
+    <t>JH/25-26 500</t>
+  </si>
+  <si>
+    <t>JH/25-26 504</t>
+  </si>
+  <si>
+    <t>JH/25-26 510</t>
+  </si>
+  <si>
+    <t>JH/25-26 511</t>
+  </si>
+  <si>
+    <t>JH/25-26 519</t>
+  </si>
+  <si>
+    <t>JH/25-26 546</t>
+  </si>
+  <si>
+    <t>JH/25-26 555</t>
+  </si>
+  <si>
+    <t>JH/25-26 556</t>
+  </si>
+  <si>
+    <t>JH/25-26 561</t>
+  </si>
+  <si>
+    <t>JH/25-26 571</t>
+  </si>
+  <si>
+    <t>JH/25-26 572</t>
+  </si>
+  <si>
+    <t>JH/25-26 586</t>
+  </si>
+  <si>
+    <t>JH/25-26 602</t>
+  </si>
+  <si>
+    <t>JH/25-26 608</t>
+  </si>
+  <si>
+    <t>JH/25-26 630</t>
+  </si>
+  <si>
+    <t>JH/25-26 631</t>
+  </si>
+  <si>
+    <t>JH/25-26 652</t>
+  </si>
+  <si>
+    <t>JH/25-26 661</t>
+  </si>
+  <si>
+    <t>JH/25-26 666</t>
+  </si>
+  <si>
+    <t>JH/25-26 680</t>
+  </si>
+  <si>
+    <t>JH/25-26 696</t>
+  </si>
+  <si>
+    <t>JH/25-26 699</t>
+  </si>
+  <si>
+    <t>JH/25-26 711</t>
+  </si>
+  <si>
+    <t>JH/25-26 713</t>
+  </si>
+  <si>
+    <t>JH/25-26 744</t>
+  </si>
+  <si>
+    <t>JH/25-26 750</t>
+  </si>
+  <si>
+    <t>JH/25-26 772</t>
+  </si>
+  <si>
+    <t>JH/25-26 787</t>
+  </si>
+  <si>
+    <t>JH/25-26 800</t>
+  </si>
+  <si>
+    <t>JH/25-26 808</t>
+  </si>
+  <si>
+    <t>JH/25-26 821</t>
+  </si>
+  <si>
+    <t>JH/25-26 826</t>
+  </si>
+  <si>
+    <t>JH/25-26 834</t>
+  </si>
+  <si>
+    <t>JH/25-26 839</t>
+  </si>
+  <si>
+    <t>JH/25-26 844</t>
+  </si>
+  <si>
+    <t>JH/25-26 855</t>
+  </si>
+  <si>
+    <t>JH/25-26 887</t>
+  </si>
+  <si>
+    <t>JH/25-26 904</t>
+  </si>
+  <si>
+    <t>JH/25-26 908</t>
+  </si>
+  <si>
+    <t>JH/25-26 917</t>
+  </si>
+  <si>
+    <t>JH/25-26 925</t>
+  </si>
+  <si>
+    <t>JH/25-26 937</t>
+  </si>
+  <si>
+    <t>JH/25-26 940</t>
+  </si>
+  <si>
+    <t>JH/25-26 945</t>
+  </si>
+  <si>
+    <t>JH/25-26 981</t>
+  </si>
+  <si>
+    <t>JH/25-26 982</t>
+  </si>
+  <si>
+    <t>JH/25-26 985</t>
+  </si>
+  <si>
+    <t>JH/25-26 989</t>
+  </si>
+  <si>
+    <t>JH/25-26 993</t>
+  </si>
+  <si>
+    <t>JH/25-26 1026</t>
+  </si>
+  <si>
+    <t>JH/25-26 1033</t>
+  </si>
+  <si>
+    <t>JH/25-26 1041</t>
+  </si>
+  <si>
+    <t>JH/25-26 1069</t>
+  </si>
+  <si>
+    <t>JH/25-26 1081</t>
+  </si>
+  <si>
+    <t>JH/25-26 1107</t>
+  </si>
+  <si>
+    <t>JH/25-26 1117</t>
+  </si>
+  <si>
+    <t>JH/25-26 1120</t>
+  </si>
+  <si>
+    <t>JH/25-26 1125</t>
+  </si>
+  <si>
+    <t>JH/25-26 1127</t>
+  </si>
+  <si>
+    <t>JH/25-26 1135</t>
+  </si>
+  <si>
+    <t>JH/25-26 1145</t>
+  </si>
+  <si>
+    <t>JH/25-26 1160</t>
+  </si>
+  <si>
+    <t>JH/25-26 1166</t>
+  </si>
+  <si>
+    <t>JH/25-26 1179</t>
+  </si>
+  <si>
+    <t>JH/25-26 1185</t>
+  </si>
+  <si>
+    <t>JH/25-26 1192</t>
+  </si>
+  <si>
+    <t>JH/25-26 1197</t>
+  </si>
+  <si>
+    <t>JH/25-26 1242</t>
+  </si>
+  <si>
+    <t>JH/25-26 1260</t>
+  </si>
+  <si>
+    <t>JH/25-26 1262</t>
+  </si>
+  <si>
+    <t>JH/25-26 1280</t>
+  </si>
+  <si>
+    <t>JH/25-26 1285</t>
+  </si>
+  <si>
+    <t>JH/25-26 1287</t>
+  </si>
+  <si>
+    <t>JH/25-26 1293</t>
+  </si>
+  <si>
+    <t>JH/25-26 1295</t>
+  </si>
+  <si>
+    <t>JH/25-26 1296</t>
+  </si>
+  <si>
+    <t>JH/25-26 1300</t>
+  </si>
+  <si>
+    <t>JH/25-26 1301</t>
+  </si>
+  <si>
+    <t>JH/25-26 1317</t>
+  </si>
+  <si>
+    <t>JH/25-26 1320</t>
+  </si>
+  <si>
+    <t>JH/25-26 1327</t>
+  </si>
+  <si>
+    <t>JH/25-26 1336</t>
+  </si>
+  <si>
+    <t>JH/25-26 1348</t>
+  </si>
+  <si>
+    <t>JH/25-26 1350</t>
+  </si>
+  <si>
+    <t>JH/25-26 1358</t>
+  </si>
+  <si>
+    <t>JH/25-26 1361</t>
+  </si>
+  <si>
+    <t>JH/25-26 1370</t>
+  </si>
+  <si>
+    <t>JH/25-26 1380</t>
+  </si>
+  <si>
+    <t>JH/25-26 1381</t>
+  </si>
+  <si>
+    <t>JH/25-26 1391</t>
+  </si>
+  <si>
+    <t>JH/25-26 1414</t>
+  </si>
+  <si>
+    <t>JH/25-26 1443</t>
+  </si>
+  <si>
+    <t>JH/25-26 1469</t>
+  </si>
+  <si>
+    <t>JH/25-26 1491</t>
+  </si>
+  <si>
+    <t>JH/25-26 1506</t>
+  </si>
+  <si>
+    <t>JH/25-26 1507</t>
+  </si>
+  <si>
+    <t>JH/25-26 1522</t>
+  </si>
+  <si>
+    <t>JH/25-26 1529</t>
+  </si>
+  <si>
+    <t>JH/25-26 1533</t>
+  </si>
+  <si>
+    <t>JH/25-26 1537</t>
+  </si>
+  <si>
+    <t>JH/25-26 1550</t>
+  </si>
+  <si>
+    <t>JH/25-26 1553</t>
+  </si>
+  <si>
+    <t>JH/25-26 1555</t>
+  </si>
+  <si>
+    <t>JH/25-26 1557</t>
+  </si>
+  <si>
+    <t>JH/25-26 1558</t>
+  </si>
+  <si>
+    <t>JH/25-26 1570</t>
+  </si>
+  <si>
+    <t>JH/25-26 1571</t>
+  </si>
+  <si>
+    <t>JH/25-26 1579</t>
+  </si>
+  <si>
+    <t>JH/25-26 1598</t>
+  </si>
+  <si>
+    <t>JH/25-26 1636</t>
+  </si>
+  <si>
+    <t>JH/25-26 1638</t>
+  </si>
+  <si>
+    <t>JH/25-26 1643</t>
+  </si>
+  <si>
+    <t>JH/25-26 1648</t>
+  </si>
+  <si>
+    <t>JH/25-26 1656</t>
+  </si>
+  <si>
+    <t>JH/25-26 1702</t>
+  </si>
+  <si>
+    <t>JH/25-26 1718</t>
+  </si>
+  <si>
+    <t>JH/25-26 1723</t>
+  </si>
+  <si>
+    <t>JH/25-26 1743</t>
+  </si>
+  <si>
+    <t>JH/25-26 1779</t>
+  </si>
+  <si>
+    <t>JH/25-26 1785</t>
+  </si>
+  <si>
+    <t>JH/25-26 1795</t>
+  </si>
+  <si>
+    <t>JH/25-26 1797</t>
+  </si>
+  <si>
+    <t>JH/25-26 1799</t>
+  </si>
+  <si>
+    <t>JH/25-26 1823</t>
+  </si>
+  <si>
+    <t>JH/25-26 1831</t>
+  </si>
+  <si>
+    <t>JH/25-26 1837</t>
+  </si>
+  <si>
+    <t>JH/25-26 1844</t>
+  </si>
+  <si>
+    <t>JH/25-26 1846</t>
+  </si>
+  <si>
+    <t>JH/25-26 1854</t>
+  </si>
+  <si>
+    <t>JH/25-26 1866</t>
+  </si>
+  <si>
+    <t>JH/25-26 1871</t>
+  </si>
+  <si>
+    <t>JH/25-26 1873</t>
+  </si>
+  <si>
+    <t>JH/25-26 1922</t>
+  </si>
+  <si>
+    <t>JH/25-26 1931</t>
+  </si>
+  <si>
+    <t>JH/25-26 1957</t>
+  </si>
+  <si>
+    <t>JH/25-26 1962</t>
+  </si>
+  <si>
+    <t>JH/25-26 1976</t>
+  </si>
+  <si>
+    <t>JH/25-26 1986</t>
+  </si>
+  <si>
+    <t>JH/25-26 1990</t>
+  </si>
+  <si>
+    <t>JH/25-26 1995</t>
+  </si>
+  <si>
+    <t>JH/25-26 2024</t>
+  </si>
+  <si>
+    <t>JH/25-26 2031</t>
+  </si>
+  <si>
+    <t>JH/25-26 2043</t>
+  </si>
+  <si>
+    <t>JH/25-26 2078</t>
+  </si>
+  <si>
+    <t>JH/25-26 2099</t>
+  </si>
+  <si>
+    <t>JH/25-26 2108</t>
+  </si>
+  <si>
+    <t>JH/25-26 2123</t>
+  </si>
+  <si>
+    <t>B-Branch Sales</t>
+  </si>
+  <si>
+    <t>XyX2RAT</t>
+  </si>
+  <si>
+    <t>Iic3SNo</t>
+  </si>
+  <si>
+    <t>G3GZ4fBOPK</t>
+  </si>
+  <si>
+    <t>DYyktb4b</t>
+  </si>
+  <si>
+    <t>TcCU1cwLT</t>
+  </si>
+  <si>
+    <t>K6kytzTk</t>
+  </si>
+  <si>
+    <t>VbF0IAgS</t>
+  </si>
+  <si>
+    <t>Loi0Uiqb</t>
+  </si>
+  <si>
+    <t>rtQWo1gYI</t>
+  </si>
+  <si>
+    <t>cKaUQCM0e</t>
+  </si>
+  <si>
+    <t>YQhSWHsb18</t>
+  </si>
+  <si>
+    <t>uih6eq</t>
+  </si>
+  <si>
+    <t>no0b5n4</t>
+  </si>
+  <si>
+    <t>3KUmOBD</t>
+  </si>
+  <si>
+    <t>ZeXmCav</t>
+  </si>
+  <si>
+    <t>M12AgVjIe</t>
+  </si>
+  <si>
+    <t>tZkEOVxxf</t>
+  </si>
+  <si>
+    <t>JhK4K06</t>
+  </si>
+  <si>
+    <t>FaQz3a9</t>
+  </si>
+  <si>
+    <t>NaJYegzU</t>
+  </si>
+  <si>
+    <t>Igcgnlwe</t>
+  </si>
+  <si>
+    <t>1Qz6QEFTU</t>
+  </si>
+  <si>
+    <t>m4DFdQV</t>
+  </si>
+  <si>
+    <t>MjMPWAU</t>
+  </si>
+  <si>
+    <t>c5cEFQ</t>
+  </si>
+  <si>
+    <t>qA1mXk</t>
+  </si>
+  <si>
+    <t>ihPMzMfn9t</t>
+  </si>
+  <si>
+    <t>q7ThAsv</t>
+  </si>
+  <si>
+    <t>k82CsqEQ</t>
+  </si>
+  <si>
+    <t>Lor3v9XyhT</t>
+  </si>
+  <si>
+    <t>K2VPaTbpu</t>
+  </si>
+  <si>
+    <t>PuRfdIBm</t>
+  </si>
+  <si>
+    <t>EsbOXV9TO</t>
+  </si>
+  <si>
+    <t>qaRJeb</t>
+  </si>
+  <si>
+    <t>VhiDLR</t>
+  </si>
+  <si>
+    <t>LUKTXX</t>
+  </si>
+  <si>
+    <t>FP9bXgPXzB</t>
+  </si>
+  <si>
+    <t>c7x3HS9fW</t>
+  </si>
+  <si>
+    <t>hszeGG</t>
+  </si>
+  <si>
+    <t>JdbfAHxx</t>
+  </si>
+  <si>
+    <t>fHfSrkJWaK</t>
+  </si>
+  <si>
+    <t>85R1GQg79</t>
+  </si>
+  <si>
+    <t>nRSJ1hgX</t>
+  </si>
+  <si>
+    <t>Cvw7Z7qHn</t>
+  </si>
+  <si>
+    <t>ibMD0r</t>
+  </si>
+  <si>
+    <t>MbuX9IKSq</t>
+  </si>
+  <si>
+    <t>gK09BM</t>
+  </si>
+  <si>
+    <t>xyIYLctFG</t>
+  </si>
+  <si>
+    <t>IUHnBmJgI3</t>
+  </si>
+  <si>
+    <t>ziBy3wo</t>
+  </si>
+  <si>
+    <t>T9lYYdHez</t>
+  </si>
+  <si>
+    <t>W84i0e</t>
+  </si>
+  <si>
+    <t>eInSCFC</t>
+  </si>
+  <si>
+    <t>W6ACBovyks</t>
+  </si>
+  <si>
+    <t>eMJFY3tj</t>
+  </si>
+  <si>
+    <t>USppDw</t>
+  </si>
+  <si>
+    <t>zoDPgm</t>
+  </si>
+  <si>
+    <t>ZXTkOvlWm</t>
+  </si>
+  <si>
+    <t>p8tpsnj5</t>
+  </si>
+  <si>
+    <t>27MertCL</t>
+  </si>
+  <si>
+    <t>fBips1k</t>
+  </si>
+  <si>
+    <t>mi9PxyN</t>
+  </si>
+  <si>
+    <t>sftiaDjy</t>
+  </si>
+  <si>
+    <t>n4QTtd9aHa</t>
+  </si>
+  <si>
+    <t>pKex8nED9X</t>
+  </si>
+  <si>
+    <t>3sNnok</t>
+  </si>
+  <si>
+    <t>8LiLxV</t>
+  </si>
+  <si>
+    <t>7hqhLhFN6</t>
+  </si>
+  <si>
+    <t>Xw3Kb4i</t>
+  </si>
+  <si>
+    <t>DVdBX8</t>
+  </si>
+  <si>
+    <t>W1u5Szo</t>
+  </si>
+  <si>
+    <t>ZbYKBFD</t>
+  </si>
+  <si>
+    <t>u2uc1CNX41</t>
+  </si>
+  <si>
+    <t>oKN8tO4</t>
+  </si>
+  <si>
+    <t>kjkH5sY</t>
+  </si>
+  <si>
+    <t>w802veLpj</t>
+  </si>
+  <si>
+    <t>SuzssFq</t>
+  </si>
+  <si>
+    <t>CW0LJ57uSh</t>
+  </si>
+  <si>
+    <t>ElNwGt</t>
+  </si>
+  <si>
+    <t>hJLZVQU</t>
+  </si>
+  <si>
+    <t>d1NBYN9HA</t>
+  </si>
+  <si>
+    <t>9NjPxalw</t>
+  </si>
+  <si>
+    <t>aRCmNog5Uf</t>
+  </si>
+  <si>
+    <t>2oQRMSfML</t>
+  </si>
+  <si>
+    <t>jpqQXk</t>
+  </si>
+  <si>
+    <t>8ns31JFm2S</t>
+  </si>
+  <si>
+    <t>fkpAXtnl</t>
+  </si>
+  <si>
+    <t>AA No-9477 1199 4617</t>
+  </si>
+  <si>
+    <t>AA No-5471 6718 9778</t>
+  </si>
+  <si>
+    <t>AA No-8713 7743 4297</t>
+  </si>
+  <si>
+    <t>AA No-8963 1773 8167</t>
+  </si>
+  <si>
+    <t>AA No-1772 6909 7165</t>
+  </si>
+  <si>
+    <t>AA No-1754 5697 6877</t>
+  </si>
+  <si>
+    <t>AA No-8669 5178 5337</t>
+  </si>
+  <si>
+    <t>AA No-1830 2458 6386</t>
+  </si>
+  <si>
+    <t>AA No-4289 7560 7675</t>
+  </si>
+  <si>
+    <t>AA No-2731 2696 7217</t>
+  </si>
+  <si>
+    <t>AA No-7622 3023 1557</t>
+  </si>
+  <si>
+    <t>AA No-9115 6736 6886</t>
+  </si>
+  <si>
+    <t>AA No-2327 2081 5054</t>
+  </si>
+  <si>
+    <t>AA No-3131 6182 3424</t>
+  </si>
+  <si>
+    <t>AA No-2669 3959 8123</t>
+  </si>
+  <si>
+    <t>AA No-2634 6983 6686</t>
+  </si>
+  <si>
+    <t>AA No-8979 6336 3210</t>
+  </si>
+  <si>
+    <t>AA No-1376 7280 4167</t>
+  </si>
+  <si>
+    <t>AA No-6709 6161 4663</t>
+  </si>
+  <si>
+    <t>AA No-9585 8816 3329</t>
+  </si>
+  <si>
+    <t>AA No-9269 7745 1351</t>
+  </si>
+  <si>
+    <t>AA No-4347 5005 6382</t>
+  </si>
+  <si>
+    <t>AA No-5864 1419 5070</t>
+  </si>
+  <si>
+    <t>AA No-4119 3624 4457</t>
+  </si>
+  <si>
+    <t>AA No-2397 2212 2550</t>
+  </si>
+  <si>
+    <t>AA No-9535 1532 6764</t>
+  </si>
+  <si>
+    <t>AA No-1089 4339 7936</t>
+  </si>
+  <si>
+    <t>AA No-3454 2875 8133</t>
+  </si>
+  <si>
+    <t>AA No-8512 4519 2469</t>
+  </si>
+  <si>
+    <t>AA No-4276 3036 3549</t>
+  </si>
+  <si>
+    <t>AA No-7861 4752 3322</t>
+  </si>
+  <si>
+    <t>AA No-6532 2943 9193</t>
+  </si>
+  <si>
+    <t>AA No-6942 5170 2028</t>
+  </si>
+  <si>
+    <t>AA No-6508 5464 7596</t>
+  </si>
+  <si>
+    <t>AA No-6933 6857 2203</t>
+  </si>
+  <si>
+    <t>AA No-7282 6260 4895</t>
+  </si>
+  <si>
+    <t>AA No-9179 6658 3687</t>
+  </si>
+  <si>
+    <t>AA No-5817 9192 2814</t>
+  </si>
+  <si>
+    <t>AA No-1236 7024 2354</t>
+  </si>
+  <si>
+    <t>AA No-3543 9935 5097</t>
+  </si>
+  <si>
+    <t>AA No-5281 2007 8513</t>
+  </si>
+  <si>
+    <t>AA No-8535 2593 9828</t>
+  </si>
+  <si>
+    <t>AA No-1143 9403 5749</t>
+  </si>
+  <si>
+    <t>AA No-6803 4951 5798</t>
+  </si>
+  <si>
+    <t>AA No-7785 3956 4318</t>
+  </si>
+  <si>
+    <t>AA No-2022 2896 6103</t>
+  </si>
+  <si>
+    <t>AA No-4369 9405 5782</t>
+  </si>
+  <si>
+    <t>AA No-1066 9321 2086</t>
+  </si>
+  <si>
+    <t>AA No-5743 7539 3381</t>
+  </si>
+  <si>
+    <t>AA No-6323 1473 6571</t>
+  </si>
+  <si>
+    <t>AA No-5805 8676 3779</t>
+  </si>
+  <si>
+    <t>AA No-3190 3974 4260</t>
+  </si>
+  <si>
+    <t>AA No-1998 8738 9895</t>
+  </si>
+  <si>
+    <t>AA No-1585 8955 3974</t>
+  </si>
+  <si>
+    <t>AA No-3312 2433 1889</t>
+  </si>
+  <si>
+    <t>AA No-8069 7161 7668</t>
+  </si>
+  <si>
+    <t>AA No-9058 2088 8456</t>
+  </si>
+  <si>
+    <t>AA No-6136 2949 2241</t>
+  </si>
+  <si>
+    <t>AA No-6271 3579 4348</t>
+  </si>
+  <si>
+    <t>AA No-4737 8291 8451</t>
+  </si>
+  <si>
+    <t>AA No-7195 5486 8439</t>
+  </si>
+  <si>
+    <t>AA No-2488 2105 2284</t>
+  </si>
+  <si>
+    <t>AA No-7288 9885 6523</t>
+  </si>
+  <si>
+    <t>AA No-7964 2307 4483</t>
+  </si>
+  <si>
+    <t>AA No-6877 5887 1045</t>
+  </si>
+  <si>
+    <t>AA No-4642 7098 4831</t>
+  </si>
+  <si>
+    <t>AA No-2340 1957 1414</t>
+  </si>
+  <si>
+    <t>AA No-9697 7068 9172</t>
+  </si>
+  <si>
+    <t>AA No-8456 6933 7320</t>
+  </si>
+  <si>
+    <t>AA No-2781 5977 6278</t>
+  </si>
+  <si>
+    <t>AA No-4335 8483 4740</t>
+  </si>
+  <si>
+    <t>AA No-9062 4418 6681</t>
+  </si>
+  <si>
+    <t>AA No-1526 5706 2225</t>
+  </si>
+  <si>
+    <t>AA No-1213 9758 8432</t>
+  </si>
+  <si>
+    <t>AA No-7026 2745 1998</t>
+  </si>
+  <si>
+    <t>AA No-9853 5864 7289</t>
+  </si>
+  <si>
+    <t>AA No-5755 2416 4641</t>
+  </si>
+  <si>
+    <t>AA No-8667 2344 1013</t>
+  </si>
+  <si>
+    <t>AA No-8476 6543 4695</t>
+  </si>
+  <si>
+    <t>AA No-7481 9544 2527</t>
+  </si>
+  <si>
+    <t>AA No-3679 2289 7567</t>
+  </si>
+  <si>
+    <t>AA No-5313 8357 9016</t>
+  </si>
+  <si>
+    <t>AA No-2613 1849 8213</t>
+  </si>
+  <si>
+    <t>AA No-1746 5619 5121</t>
+  </si>
+  <si>
+    <t>AA No-7627 7501 5692</t>
+  </si>
+  <si>
+    <t>AA No-7029 7791 3695</t>
+  </si>
+  <si>
+    <t>AA No-1323 8874 3198</t>
+  </si>
+  <si>
+    <t>AA No-7535 2332 2977</t>
+  </si>
+  <si>
+    <t>AA No-8923 9276 7220</t>
+  </si>
+  <si>
+    <t>AA No-4271 1883 5363</t>
+  </si>
+  <si>
+    <t>AA No-5819 7537 9145</t>
+  </si>
+  <si>
+    <t>AA No-4786 2257 3246</t>
+  </si>
+  <si>
+    <t>AA No-5602 1700 7545</t>
+  </si>
+  <si>
+    <t>AA No-2421 6113 8287</t>
+  </si>
+  <si>
+    <t>AA No-8366 8961 2215</t>
+  </si>
+  <si>
+    <t>AA No-3334 8981 5603</t>
+  </si>
+  <si>
+    <t>AA No-9148 7127 4199</t>
+  </si>
+  <si>
+    <t>AA No-5286 1551 2644</t>
+  </si>
+  <si>
+    <t>AA No-3687 5709 5359</t>
+  </si>
+  <si>
+    <t>AA No-8774 1789 7740</t>
+  </si>
+  <si>
+    <t>AA No-1375 9745 9771</t>
+  </si>
+  <si>
+    <t>AA No-1030 1124 4389</t>
+  </si>
+  <si>
+    <t>AA No-2381 4876 1483</t>
+  </si>
+  <si>
+    <t>AA No-4209 5534 2602</t>
+  </si>
+  <si>
+    <t>AA No-1166 8513 9043</t>
+  </si>
+  <si>
+    <t>AA No:4675 2309 5377</t>
+  </si>
+  <si>
+    <t>AA No:1101 1203 5748</t>
+  </si>
+  <si>
+    <t>AA No:4556 4434 6259</t>
+  </si>
+  <si>
+    <t>AA No:4029 1665 7759</t>
+  </si>
+  <si>
+    <t>AA No:7740 7415 2584</t>
+  </si>
+  <si>
+    <t>AA No:4463 9265 4998</t>
+  </si>
+  <si>
+    <t>AA No:4184 6390 2078</t>
+  </si>
+  <si>
+    <t>AA No:8953 9179 5363</t>
+  </si>
+  <si>
+    <t>AA No:9390 5546 3596</t>
+  </si>
+  <si>
+    <t>AA No:5488 2536 7738</t>
+  </si>
+  <si>
+    <t>AA No:4626 8147 3006</t>
+  </si>
+  <si>
+    <t>AA No:1818 7946 8739</t>
+  </si>
+  <si>
+    <t>AA No:6467 6137 4721</t>
+  </si>
+  <si>
+    <t>AA No:2789 9516 5719</t>
+  </si>
+  <si>
+    <t>AA No:5094 8216 3450</t>
+  </si>
+  <si>
+    <t>AA No:2426 4632 3817</t>
+  </si>
+  <si>
+    <t>AA No:3693 5647 4504</t>
+  </si>
+  <si>
+    <t>AA No:2425 9244 7244</t>
+  </si>
+  <si>
+    <t>AA No:1922 5167 7807</t>
+  </si>
+  <si>
+    <t>AA No:3815 3954 3647</t>
+  </si>
+  <si>
+    <t>AA No:1099 3604 3167</t>
+  </si>
+  <si>
+    <t>AA No:8010 2670 4022</t>
+  </si>
+  <si>
+    <t>AA No:8373 9353 3387</t>
+  </si>
+  <si>
+    <t>AA No:3455 7455 7768</t>
+  </si>
+  <si>
+    <t>AA No:6847 3248 5797</t>
+  </si>
+  <si>
+    <t>AA No:5516 9850 6208</t>
+  </si>
+  <si>
+    <t>AA No:8269 5546 7172</t>
+  </si>
+  <si>
+    <t>AA No:2426 9080 4321</t>
+  </si>
+  <si>
+    <t>AA No:5031 8829 1853</t>
+  </si>
+  <si>
+    <t>AA No:4153 6577 4151</t>
+  </si>
+  <si>
+    <t>AA No:2512 4739 5257</t>
+  </si>
+  <si>
+    <t>AA No:2964 9054 4880</t>
+  </si>
+  <si>
+    <t>AA No:9658 4678 1877</t>
+  </si>
+  <si>
+    <t>AA No:9493 2349 3525</t>
+  </si>
+  <si>
+    <t>AA No:3661 4825 9172</t>
+  </si>
+  <si>
+    <t>AA No:1166 6369 7445</t>
+  </si>
+  <si>
+    <t>AA No:1563 3871 9664</t>
+  </si>
+  <si>
+    <t>AA No:1987 7916 4860</t>
+  </si>
+  <si>
+    <t>AA No:5576 7269 7108</t>
+  </si>
+  <si>
+    <t>AA No:9277 1817 1052</t>
+  </si>
+  <si>
+    <t>AA No:6590 4640 2260</t>
+  </si>
+  <si>
+    <t>AA No:2427 4096 5802</t>
+  </si>
+  <si>
+    <t>AA No:1822 8709 4568</t>
+  </si>
+  <si>
+    <t>AA No:2220 4119 1436</t>
+  </si>
+  <si>
+    <t>AA No:3241 6763 5695</t>
+  </si>
+  <si>
+    <t>AA No:5151 2331 9680</t>
+  </si>
+  <si>
+    <t>AA No:4425 1143 1816</t>
+  </si>
+  <si>
+    <t>AA No:9092 1826 6376</t>
+  </si>
+  <si>
+    <t>AA No:9240 2121 2297</t>
+  </si>
+  <si>
+    <t>AA No:2793 6319 4389</t>
+  </si>
+  <si>
+    <t>AA No:1427 2969 4387</t>
+  </si>
+  <si>
+    <t>AA No:1591 7468 9402</t>
+  </si>
+  <si>
+    <t>AA No:1107 5949 7379</t>
+  </si>
+  <si>
+    <t>AA No:9438 2432 7176</t>
+  </si>
+  <si>
+    <t>AA No:9652 8044 7637</t>
+  </si>
+  <si>
+    <t>AA No:1614 1037 1757</t>
+  </si>
+  <si>
+    <t>AA No:2264 2306 9772</t>
+  </si>
+  <si>
+    <t>AA No:5389 2445 2402</t>
+  </si>
+  <si>
+    <t>AA No:7644 1528 8028</t>
+  </si>
+  <si>
+    <t>AA No:6723 7273 5783</t>
+  </si>
+  <si>
+    <t>AA No:6395 8989 9766</t>
+  </si>
+  <si>
+    <t>AA No:9763 7871 6999</t>
+  </si>
+  <si>
+    <t>AA No:6247 4453 9164</t>
+  </si>
+  <si>
+    <t>AA No:1967 2960 3717</t>
+  </si>
+  <si>
+    <t>AA No:2264 2300 2712</t>
+  </si>
+  <si>
+    <t>AA No:5433 8821 4934</t>
+  </si>
+  <si>
+    <t>AA No:5387 6880 3923</t>
+  </si>
+  <si>
+    <t>AA No:6104 5504 1248</t>
+  </si>
+  <si>
+    <t>AA No:8859 4178 4050</t>
+  </si>
+  <si>
+    <t>AA No:9373 1469 4948</t>
+  </si>
+  <si>
+    <t>AA No:5871 6940 4633</t>
+  </si>
+  <si>
+    <t>AA No:9308 6359 3343</t>
+  </si>
+  <si>
+    <t>AA No:9674 5839 8243</t>
+  </si>
+  <si>
+    <t>AA No:5620 6053 6608</t>
+  </si>
+  <si>
+    <t>AA No:1192 4234 3489</t>
+  </si>
+  <si>
+    <t>AA No:2193 4875 5659</t>
+  </si>
+  <si>
+    <t>AA No:5369 2087 9410</t>
+  </si>
+  <si>
+    <t>AA No:1043 7759 2691</t>
+  </si>
+  <si>
+    <t>AA No:8642 9433 1812</t>
+  </si>
+  <si>
+    <t>AA No:7695 1242 3740</t>
+  </si>
+  <si>
+    <t>AA No:9615 6379 7435</t>
+  </si>
+  <si>
+    <t>AA No:9063 5716 2096</t>
+  </si>
+  <si>
+    <t>AA No:3414 4068 7056</t>
+  </si>
+  <si>
+    <t>AA No:6620 3805 9612</t>
+  </si>
+  <si>
+    <t>AA No:5683 2442 7682</t>
+  </si>
+  <si>
+    <t>AA No:5712 5853 1704</t>
+  </si>
+  <si>
+    <t>AA No:1441 3666 4751</t>
+  </si>
+  <si>
+    <t>AA No:7833 4201 6665</t>
+  </si>
+  <si>
+    <t>AA No:8469 5783 6532</t>
+  </si>
+  <si>
+    <t>AA No:2294 7109 7469</t>
+  </si>
+  <si>
+    <t>AA No:6673 8157 5756</t>
+  </si>
+  <si>
+    <t>AA No:7751 6911 2239</t>
+  </si>
+  <si>
+    <t>AA No:8846 3531 2973</t>
+  </si>
+  <si>
+    <t>AA No:9527 9933 3928</t>
+  </si>
+  <si>
+    <t>AA No:4867 6403 5469</t>
   </si>
   <si>
     <t>['MISSING_PAN_ABOVE_2L']</t>
   </si>
   <si>
-    <t>['MISSING_ADDRESS_PROOF_ABOVE_50K']</t>
+    <t>['INVALID_PAN_FORMAT']</t>
   </si>
   <si>
     <t>['No valid PAN found in PAN or PAN1 columns']</t>
-  </si>
-  <si>
-    <t>['Address proof missing in both address proof columns']</t>
   </si>
 </sst>
 </file>
@@ -603,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -643,626 +1981,5463 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>241</v>
       </c>
       <c r="E2">
-        <v>669500</v>
-      </c>
-      <c r="H2" t="s">
-        <v>69</v>
+        <v>229989.03</v>
+      </c>
+      <c r="I2" t="s">
+        <v>434</v>
       </c>
       <c r="J2" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="E3">
-        <v>1022000</v>
+        <v>203934.53</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>329</v>
       </c>
       <c r="J3" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>241</v>
       </c>
       <c r="E4">
-        <v>1542000</v>
+        <v>216616.99</v>
+      </c>
+      <c r="F4" t="s">
+        <v>242</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>330</v>
       </c>
       <c r="J4" t="s">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>241</v>
       </c>
       <c r="E5">
-        <v>18790000</v>
+        <v>304247.76</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>243</v>
+      </c>
+      <c r="H5" t="s">
+        <v>331</v>
       </c>
       <c r="J5" t="s">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="K5" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="E6">
-        <v>13683611</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
+        <v>308372.52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>435</v>
       </c>
       <c r="J6" t="s">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="K6" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>241</v>
       </c>
       <c r="E7">
-        <v>475000</v>
-      </c>
-      <c r="H7" t="s">
-        <v>72</v>
+        <v>258101.82</v>
+      </c>
+      <c r="F7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I7" t="s">
+        <v>436</v>
       </c>
       <c r="J7" t="s">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="K7" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="E8">
-        <v>1065000</v>
-      </c>
-      <c r="H8" t="s">
-        <v>73</v>
+        <v>251639.06</v>
+      </c>
+      <c r="I8" t="s">
+        <v>437</v>
       </c>
       <c r="J8" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="E9">
-        <v>570000</v>
-      </c>
-      <c r="H9" t="s">
-        <v>74</v>
+        <v>205416.61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>245</v>
+      </c>
+      <c r="I9" t="s">
+        <v>438</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="K9" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>358</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>241</v>
       </c>
       <c r="E10">
-        <v>1255000</v>
-      </c>
-      <c r="H10" t="s">
-        <v>75</v>
+        <v>205305.84</v>
+      </c>
+      <c r="I10" t="s">
+        <v>439</v>
       </c>
       <c r="J10" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K10" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>366</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>241</v>
       </c>
       <c r="E11">
-        <v>564999.98</v>
-      </c>
-      <c r="H11" t="s">
-        <v>76</v>
+        <v>279368.34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>440</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>527</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
       <c r="E12">
-        <v>2240000</v>
-      </c>
-      <c r="H12" t="s">
-        <v>77</v>
+        <v>201270.24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>441</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>701</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>241</v>
       </c>
       <c r="E13">
-        <v>937000</v>
+        <v>304513.42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>246</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>745</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="E14">
-        <v>545000</v>
+        <v>235999.11</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>333</v>
       </c>
       <c r="J14" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>747</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>241</v>
       </c>
       <c r="E15">
-        <v>984999.99</v>
+        <v>282178.37</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>852</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="E16">
-        <v>38547472</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
+        <v>284259.83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>335</v>
       </c>
       <c r="J16" t="s">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="K16" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>853</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="E17">
-        <v>15472753</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
+        <v>251430.63</v>
+      </c>
+      <c r="I17" t="s">
+        <v>442</v>
       </c>
       <c r="J17" t="s">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="K17" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>1011</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="E18">
-        <v>865000</v>
+        <v>267130.86</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="J18" t="s">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>1047</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="E19">
-        <v>400000</v>
-      </c>
-      <c r="H19" t="s">
-        <v>81</v>
+        <v>232157.55</v>
+      </c>
+      <c r="F19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I19" t="s">
+        <v>443</v>
       </c>
       <c r="J19" t="s">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="K19" t="s">
-        <v>84</v>
+        <v>531</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>1107</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="E20">
-        <v>1537792</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
+        <v>247751.82</v>
+      </c>
+      <c r="H20" t="s">
+        <v>337</v>
       </c>
       <c r="J20" t="s">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="K20" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>1167</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="E21">
-        <v>5577000</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
+        <v>277482.61</v>
+      </c>
+      <c r="H21" t="s">
+        <v>338</v>
       </c>
       <c r="J21" t="s">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="K21" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>1168</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="E22">
-        <v>56788</v>
+        <v>287920.35</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>248</v>
+      </c>
+      <c r="I22" t="s">
+        <v>444</v>
       </c>
       <c r="J22" t="s">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>1169</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="E23">
-        <v>54783</v>
+        <v>304634.41</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>249</v>
+      </c>
+      <c r="I23" t="s">
+        <v>445</v>
       </c>
       <c r="J23" t="s">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="K23" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>1173</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="E24">
-        <v>1474129</v>
+        <v>253959.18</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>250</v>
+      </c>
+      <c r="I24" t="s">
+        <v>446</v>
       </c>
       <c r="J24" t="s">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="K24" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>1174</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E25">
+        <v>242630.82</v>
+      </c>
+      <c r="I25" t="s">
+        <v>447</v>
+      </c>
+      <c r="J25" t="s">
+        <v>529</v>
+      </c>
+      <c r="K25" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26">
+        <v>301</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26">
+        <v>253275.7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>251</v>
+      </c>
+      <c r="H26" t="s">
+        <v>339</v>
+      </c>
+      <c r="J26" t="s">
+        <v>530</v>
+      </c>
+      <c r="K26" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27">
+        <v>302</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27">
+        <v>239189.38</v>
+      </c>
+      <c r="H27" t="s">
+        <v>340</v>
+      </c>
+      <c r="J27" t="s">
+        <v>529</v>
+      </c>
+      <c r="K27" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28">
+        <v>306</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E28">
+        <v>245260.62</v>
+      </c>
+      <c r="I28" t="s">
+        <v>448</v>
+      </c>
+      <c r="J28" t="s">
+        <v>529</v>
+      </c>
+      <c r="K28" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29">
+        <v>317</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29">
+        <v>305061.23</v>
+      </c>
+      <c r="H29" t="s">
+        <v>341</v>
+      </c>
+      <c r="J29" t="s">
+        <v>529</v>
+      </c>
+      <c r="K29" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>322</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30">
+        <v>204637.48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>252</v>
+      </c>
+      <c r="H30" t="s">
+        <v>342</v>
+      </c>
+      <c r="J30" t="s">
+        <v>530</v>
+      </c>
+      <c r="K30" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31">
+        <v>327</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31">
+        <v>235895.11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>253</v>
+      </c>
+      <c r="I31" t="s">
+        <v>449</v>
+      </c>
+      <c r="J31" t="s">
+        <v>530</v>
+      </c>
+      <c r="K31" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>333</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32">
+        <v>307582.7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>343</v>
+      </c>
+      <c r="J32" t="s">
+        <v>529</v>
+      </c>
+      <c r="K32" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>335</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33">
+        <v>278285.13</v>
+      </c>
+      <c r="I33" t="s">
+        <v>450</v>
+      </c>
+      <c r="J33" t="s">
+        <v>529</v>
+      </c>
+      <c r="K33" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34">
+        <v>336</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34">
+        <v>219303.62</v>
+      </c>
+      <c r="I34" t="s">
+        <v>451</v>
+      </c>
+      <c r="J34" t="s">
+        <v>529</v>
+      </c>
+      <c r="K34" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35">
+        <v>352</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35">
+        <v>207639.93</v>
+      </c>
+      <c r="I35" t="s">
+        <v>452</v>
+      </c>
+      <c r="J35" t="s">
+        <v>529</v>
+      </c>
+      <c r="K35" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36">
+        <v>355</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36">
+        <v>256786.48</v>
+      </c>
+      <c r="I36" t="s">
+        <v>453</v>
+      </c>
+      <c r="J36" t="s">
+        <v>529</v>
+      </c>
+      <c r="K36" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37">
+        <v>357</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37">
+        <v>262901.44</v>
+      </c>
+      <c r="F37" t="s">
+        <v>254</v>
+      </c>
+      <c r="I37" t="s">
+        <v>454</v>
+      </c>
+      <c r="J37" t="s">
+        <v>530</v>
+      </c>
+      <c r="K37" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>359</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38">
+        <v>273136.3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>255</v>
+      </c>
+      <c r="H38" t="s">
+        <v>344</v>
+      </c>
+      <c r="J38" t="s">
+        <v>530</v>
+      </c>
+      <c r="K38" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>362</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39">
+        <v>221666.34</v>
+      </c>
+      <c r="F39" t="s">
+        <v>256</v>
+      </c>
+      <c r="H39" t="s">
+        <v>345</v>
+      </c>
+      <c r="J39" t="s">
+        <v>530</v>
+      </c>
+      <c r="K39" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>370</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40">
+        <v>228769.68</v>
+      </c>
+      <c r="H40" t="s">
+        <v>346</v>
+      </c>
+      <c r="J40" t="s">
+        <v>529</v>
+      </c>
+      <c r="K40" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>376</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41">
+        <v>297173.27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" t="s">
+        <v>455</v>
+      </c>
+      <c r="J41" t="s">
+        <v>530</v>
+      </c>
+      <c r="K41" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>382</v>
+      </c>
+      <c r="B42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42">
+        <v>305823.28</v>
+      </c>
+      <c r="H42" t="s">
+        <v>347</v>
+      </c>
+      <c r="J42" t="s">
+        <v>529</v>
+      </c>
+      <c r="K42" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43">
+        <v>384</v>
+      </c>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43">
+        <v>264978.61</v>
+      </c>
+      <c r="I43" t="s">
+        <v>456</v>
+      </c>
+      <c r="J43" t="s">
+        <v>529</v>
+      </c>
+      <c r="K43" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44">
+        <v>386</v>
+      </c>
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" t="s">
+        <v>241</v>
+      </c>
+      <c r="E44">
+        <v>247959.74</v>
+      </c>
+      <c r="H44" t="s">
+        <v>348</v>
+      </c>
+      <c r="J44" t="s">
+        <v>529</v>
+      </c>
+      <c r="K44" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>402</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" t="s">
+        <v>241</v>
+      </c>
+      <c r="E45">
+        <v>292828.23</v>
+      </c>
+      <c r="I45" t="s">
+        <v>457</v>
+      </c>
+      <c r="J45" t="s">
+        <v>529</v>
+      </c>
+      <c r="K45" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>403</v>
+      </c>
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E46">
+        <v>224921.54</v>
+      </c>
+      <c r="I46" t="s">
+        <v>458</v>
+      </c>
+      <c r="J46" t="s">
+        <v>529</v>
+      </c>
+      <c r="K46" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>422</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47">
+        <v>263556.69</v>
+      </c>
+      <c r="H47" t="s">
+        <v>349</v>
+      </c>
+      <c r="J47" t="s">
+        <v>529</v>
+      </c>
+      <c r="K47" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>432</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48">
+        <v>275058.69</v>
+      </c>
+      <c r="F48" t="s">
+        <v>258</v>
+      </c>
+      <c r="I48" t="s">
+        <v>459</v>
+      </c>
+      <c r="J48" t="s">
+        <v>530</v>
+      </c>
+      <c r="K48" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49">
+        <v>447</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49">
+        <v>282440.17</v>
+      </c>
+      <c r="H49" t="s">
+        <v>350</v>
+      </c>
+      <c r="J49" t="s">
+        <v>529</v>
+      </c>
+      <c r="K49" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50">
+        <v>453</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E50">
+        <v>223114.96</v>
+      </c>
+      <c r="I50" t="s">
+        <v>460</v>
+      </c>
+      <c r="J50" t="s">
+        <v>529</v>
+      </c>
+      <c r="K50" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>458</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51">
+        <v>281922.26</v>
+      </c>
+      <c r="I51" t="s">
+        <v>461</v>
+      </c>
+      <c r="J51" t="s">
+        <v>529</v>
+      </c>
+      <c r="K51" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52">
+        <v>468</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52">
+        <v>267718.54</v>
+      </c>
+      <c r="F52" t="s">
+        <v>259</v>
+      </c>
+      <c r="H52" t="s">
+        <v>351</v>
+      </c>
+      <c r="J52" t="s">
+        <v>530</v>
+      </c>
+      <c r="K52" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53">
+        <v>490</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E53">
+        <v>308376.48</v>
+      </c>
+      <c r="H53" t="s">
+        <v>352</v>
+      </c>
+      <c r="J53" t="s">
+        <v>529</v>
+      </c>
+      <c r="K53" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>504</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" t="s">
+        <v>241</v>
+      </c>
+      <c r="E54">
+        <v>286753.29</v>
+      </c>
+      <c r="I54" t="s">
+        <v>462</v>
+      </c>
+      <c r="J54" t="s">
+        <v>529</v>
+      </c>
+      <c r="K54" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>506</v>
+      </c>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55">
+        <v>297870.92</v>
+      </c>
+      <c r="H55" t="s">
+        <v>353</v>
+      </c>
+      <c r="J55" t="s">
+        <v>529</v>
+      </c>
+      <c r="K55" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>510</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" t="s">
+        <v>241</v>
+      </c>
+      <c r="E56">
+        <v>272842.78</v>
+      </c>
+      <c r="F56" t="s">
+        <v>260</v>
+      </c>
+      <c r="I56" t="s">
+        <v>463</v>
+      </c>
+      <c r="J56" t="s">
+        <v>530</v>
+      </c>
+      <c r="K56" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>516</v>
+      </c>
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" t="s">
+        <v>241</v>
+      </c>
+      <c r="E57">
+        <v>279287.04</v>
+      </c>
+      <c r="I57" t="s">
+        <v>464</v>
+      </c>
+      <c r="J57" t="s">
+        <v>529</v>
+      </c>
+      <c r="K57" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>517</v>
+      </c>
+      <c r="B58" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" t="s">
+        <v>241</v>
+      </c>
+      <c r="E58">
+        <v>251496.31</v>
+      </c>
+      <c r="F58" t="s">
+        <v>261</v>
+      </c>
+      <c r="I58" t="s">
+        <v>465</v>
+      </c>
+      <c r="J58" t="s">
+        <v>530</v>
+      </c>
+      <c r="K58" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>525</v>
+      </c>
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" t="s">
+        <v>241</v>
+      </c>
+      <c r="E59">
+        <v>237947.97</v>
+      </c>
+      <c r="I59" t="s">
+        <v>466</v>
+      </c>
+      <c r="J59" t="s">
+        <v>529</v>
+      </c>
+      <c r="K59" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>552</v>
+      </c>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>99</v>
+      </c>
+      <c r="D60" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60">
+        <v>243411.62</v>
+      </c>
+      <c r="F60" t="s">
+        <v>262</v>
+      </c>
+      <c r="I60" t="s">
+        <v>467</v>
+      </c>
+      <c r="J60" t="s">
+        <v>530</v>
+      </c>
+      <c r="K60" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>561</v>
+      </c>
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" t="s">
+        <v>241</v>
+      </c>
+      <c r="E61">
+        <v>231345.54</v>
+      </c>
+      <c r="H61" t="s">
+        <v>354</v>
+      </c>
+      <c r="J61" t="s">
+        <v>529</v>
+      </c>
+      <c r="K61" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>562</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" t="s">
+        <v>241</v>
+      </c>
+      <c r="E62">
+        <v>279113.35</v>
+      </c>
+      <c r="F62" t="s">
+        <v>263</v>
+      </c>
+      <c r="H62" t="s">
+        <v>355</v>
+      </c>
+      <c r="J62" t="s">
+        <v>530</v>
+      </c>
+      <c r="K62" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>567</v>
+      </c>
+      <c r="B63" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63">
+        <v>249815.73</v>
+      </c>
+      <c r="F63" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" t="s">
+        <v>468</v>
+      </c>
+      <c r="J63" t="s">
+        <v>530</v>
+      </c>
+      <c r="K63" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>577</v>
+      </c>
+      <c r="B64" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" t="s">
+        <v>103</v>
+      </c>
+      <c r="D64" t="s">
+        <v>241</v>
+      </c>
+      <c r="E64">
+        <v>298837.1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>265</v>
+      </c>
+      <c r="I64" t="s">
+        <v>469</v>
+      </c>
+      <c r="J64" t="s">
+        <v>530</v>
+      </c>
+      <c r="K64" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>578</v>
+      </c>
+      <c r="B65" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" t="s">
+        <v>104</v>
+      </c>
+      <c r="D65" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65">
+        <v>284795.01</v>
+      </c>
+      <c r="H65" t="s">
+        <v>356</v>
+      </c>
+      <c r="J65" t="s">
+        <v>529</v>
+      </c>
+      <c r="K65" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>592</v>
+      </c>
+      <c r="B66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" t="s">
+        <v>105</v>
+      </c>
+      <c r="D66" t="s">
+        <v>241</v>
+      </c>
+      <c r="E66">
+        <v>211233.78</v>
+      </c>
+      <c r="F66" t="s">
+        <v>266</v>
+      </c>
+      <c r="I66" t="s">
+        <v>470</v>
+      </c>
+      <c r="J66" t="s">
+        <v>530</v>
+      </c>
+      <c r="K66" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>608</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" t="s">
+        <v>241</v>
+      </c>
+      <c r="E67">
+        <v>259278.52</v>
+      </c>
+      <c r="F67" t="s">
+        <v>267</v>
+      </c>
+      <c r="H67" t="s">
+        <v>357</v>
+      </c>
+      <c r="J67" t="s">
+        <v>530</v>
+      </c>
+      <c r="K67" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>614</v>
+      </c>
+      <c r="B68" t="s">
         <v>23</v>
       </c>
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25">
-        <v>9295000</v>
-      </c>
-      <c r="F25" t="s">
-        <v>68</v>
-      </c>
-      <c r="J25" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" t="s">
-        <v>85</v>
+      <c r="C68" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68">
+        <v>305914.66</v>
+      </c>
+      <c r="H68" t="s">
+        <v>358</v>
+      </c>
+      <c r="J68" t="s">
+        <v>529</v>
+      </c>
+      <c r="K68" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>636</v>
+      </c>
+      <c r="B69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69" t="s">
+        <v>241</v>
+      </c>
+      <c r="E69">
+        <v>246024.37</v>
+      </c>
+      <c r="I69" t="s">
+        <v>471</v>
+      </c>
+      <c r="J69" t="s">
+        <v>529</v>
+      </c>
+      <c r="K69" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>637</v>
+      </c>
+      <c r="B70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" t="s">
+        <v>109</v>
+      </c>
+      <c r="D70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E70">
+        <v>277595.79</v>
+      </c>
+      <c r="H70" t="s">
+        <v>359</v>
+      </c>
+      <c r="J70" t="s">
+        <v>529</v>
+      </c>
+      <c r="K70" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>658</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71">
+        <v>252511.47</v>
+      </c>
+      <c r="F71" t="s">
+        <v>268</v>
+      </c>
+      <c r="I71" t="s">
+        <v>472</v>
+      </c>
+      <c r="J71" t="s">
+        <v>530</v>
+      </c>
+      <c r="K71" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>667</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>111</v>
+      </c>
+      <c r="D72" t="s">
+        <v>241</v>
+      </c>
+      <c r="E72">
+        <v>239245.9</v>
+      </c>
+      <c r="F72" t="s">
+        <v>269</v>
+      </c>
+      <c r="H72" t="s">
+        <v>360</v>
+      </c>
+      <c r="J72" t="s">
+        <v>530</v>
+      </c>
+      <c r="K72" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>672</v>
+      </c>
+      <c r="B73" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
+        <v>241</v>
+      </c>
+      <c r="E73">
+        <v>278060.87</v>
+      </c>
+      <c r="F73" t="s">
+        <v>270</v>
+      </c>
+      <c r="H73" t="s">
+        <v>361</v>
+      </c>
+      <c r="J73" t="s">
+        <v>530</v>
+      </c>
+      <c r="K73" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>686</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" t="s">
+        <v>113</v>
+      </c>
+      <c r="D74" t="s">
+        <v>241</v>
+      </c>
+      <c r="E74">
+        <v>291047.77</v>
+      </c>
+      <c r="I74" t="s">
+        <v>473</v>
+      </c>
+      <c r="J74" t="s">
+        <v>529</v>
+      </c>
+      <c r="K74" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>702</v>
+      </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" t="s">
+        <v>241</v>
+      </c>
+      <c r="E75">
+        <v>277996.61</v>
+      </c>
+      <c r="F75" t="s">
+        <v>271</v>
+      </c>
+      <c r="I75" t="s">
+        <v>474</v>
+      </c>
+      <c r="J75" t="s">
+        <v>530</v>
+      </c>
+      <c r="K75" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>705</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" t="s">
+        <v>115</v>
+      </c>
+      <c r="D76" t="s">
+        <v>241</v>
+      </c>
+      <c r="E76">
+        <v>230600.07</v>
+      </c>
+      <c r="F76" t="s">
+        <v>272</v>
+      </c>
+      <c r="H76" t="s">
+        <v>362</v>
+      </c>
+      <c r="J76" t="s">
+        <v>530</v>
+      </c>
+      <c r="K76" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>717</v>
+      </c>
+      <c r="B77" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77" t="s">
+        <v>241</v>
+      </c>
+      <c r="E77">
+        <v>300852.53</v>
+      </c>
+      <c r="F77" t="s">
+        <v>273</v>
+      </c>
+      <c r="H77" t="s">
+        <v>363</v>
+      </c>
+      <c r="J77" t="s">
+        <v>530</v>
+      </c>
+      <c r="K77" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>719</v>
+      </c>
+      <c r="B78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" t="s">
+        <v>117</v>
+      </c>
+      <c r="D78" t="s">
+        <v>241</v>
+      </c>
+      <c r="E78">
+        <v>263674.28</v>
+      </c>
+      <c r="H78" t="s">
+        <v>364</v>
+      </c>
+      <c r="J78" t="s">
+        <v>529</v>
+      </c>
+      <c r="K78" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>750</v>
+      </c>
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" t="s">
+        <v>118</v>
+      </c>
+      <c r="D79" t="s">
+        <v>241</v>
+      </c>
+      <c r="E79">
+        <v>289005.69</v>
+      </c>
+      <c r="F79" t="s">
+        <v>274</v>
+      </c>
+      <c r="H79" t="s">
+        <v>365</v>
+      </c>
+      <c r="J79" t="s">
+        <v>530</v>
+      </c>
+      <c r="K79" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>756</v>
+      </c>
+      <c r="B80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" t="s">
+        <v>119</v>
+      </c>
+      <c r="D80" t="s">
+        <v>241</v>
+      </c>
+      <c r="E80">
+        <v>283012.91</v>
+      </c>
+      <c r="H80" t="s">
+        <v>366</v>
+      </c>
+      <c r="J80" t="s">
+        <v>529</v>
+      </c>
+      <c r="K80" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>778</v>
+      </c>
+      <c r="B81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" t="s">
+        <v>241</v>
+      </c>
+      <c r="E81">
+        <v>308604.22</v>
+      </c>
+      <c r="F81" t="s">
+        <v>275</v>
+      </c>
+      <c r="I81" t="s">
+        <v>475</v>
+      </c>
+      <c r="J81" t="s">
+        <v>530</v>
+      </c>
+      <c r="K81" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>793</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>121</v>
+      </c>
+      <c r="D82" t="s">
+        <v>241</v>
+      </c>
+      <c r="E82">
+        <v>201835.61</v>
+      </c>
+      <c r="I82" t="s">
+        <v>476</v>
+      </c>
+      <c r="J82" t="s">
+        <v>529</v>
+      </c>
+      <c r="K82" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>806</v>
+      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" t="s">
+        <v>122</v>
+      </c>
+      <c r="D83" t="s">
+        <v>241</v>
+      </c>
+      <c r="E83">
+        <v>263833.93</v>
+      </c>
+      <c r="H83" t="s">
+        <v>367</v>
+      </c>
+      <c r="J83" t="s">
+        <v>529</v>
+      </c>
+      <c r="K83" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>814</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>123</v>
+      </c>
+      <c r="D84" t="s">
+        <v>241</v>
+      </c>
+      <c r="E84">
+        <v>274731.86</v>
+      </c>
+      <c r="I84" t="s">
+        <v>477</v>
+      </c>
+      <c r="J84" t="s">
+        <v>529</v>
+      </c>
+      <c r="K84" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>827</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" t="s">
+        <v>241</v>
+      </c>
+      <c r="E85">
+        <v>213118.74</v>
+      </c>
+      <c r="F85" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" t="s">
+        <v>368</v>
+      </c>
+      <c r="J85" t="s">
+        <v>530</v>
+      </c>
+      <c r="K85" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>832</v>
+      </c>
+      <c r="B86" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" t="s">
+        <v>241</v>
+      </c>
+      <c r="E86">
+        <v>268513.28</v>
+      </c>
+      <c r="F86" t="s">
+        <v>277</v>
+      </c>
+      <c r="I86" t="s">
+        <v>478</v>
+      </c>
+      <c r="J86" t="s">
+        <v>530</v>
+      </c>
+      <c r="K86" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>840</v>
+      </c>
+      <c r="B87" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" t="s">
+        <v>241</v>
+      </c>
+      <c r="E87">
+        <v>223854.61</v>
+      </c>
+      <c r="F87" t="s">
+        <v>278</v>
+      </c>
+      <c r="H87" t="s">
+        <v>369</v>
+      </c>
+      <c r="J87" t="s">
+        <v>530</v>
+      </c>
+      <c r="K87" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88">
+        <v>845</v>
+      </c>
+      <c r="B88" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" t="s">
+        <v>127</v>
+      </c>
+      <c r="D88" t="s">
+        <v>241</v>
+      </c>
+      <c r="E88">
+        <v>218175.21</v>
+      </c>
+      <c r="I88" t="s">
+        <v>479</v>
+      </c>
+      <c r="J88" t="s">
+        <v>529</v>
+      </c>
+      <c r="K88" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89">
+        <v>850</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" t="s">
+        <v>241</v>
+      </c>
+      <c r="E89">
+        <v>200475.09</v>
+      </c>
+      <c r="F89" t="s">
+        <v>279</v>
+      </c>
+      <c r="H89" t="s">
+        <v>370</v>
+      </c>
+      <c r="J89" t="s">
+        <v>530</v>
+      </c>
+      <c r="K89" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90">
+        <v>861</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" t="s">
+        <v>129</v>
+      </c>
+      <c r="D90" t="s">
+        <v>241</v>
+      </c>
+      <c r="E90">
+        <v>205080.08</v>
+      </c>
+      <c r="F90" t="s">
+        <v>280</v>
+      </c>
+      <c r="H90" t="s">
+        <v>371</v>
+      </c>
+      <c r="J90" t="s">
+        <v>530</v>
+      </c>
+      <c r="K90" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91">
+        <v>893</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" t="s">
+        <v>241</v>
+      </c>
+      <c r="E91">
+        <v>214446.64</v>
+      </c>
+      <c r="F91" t="s">
+        <v>281</v>
+      </c>
+      <c r="H91" t="s">
+        <v>372</v>
+      </c>
+      <c r="J91" t="s">
+        <v>530</v>
+      </c>
+      <c r="K91" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92">
+        <v>910</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>131</v>
+      </c>
+      <c r="D92" t="s">
+        <v>241</v>
+      </c>
+      <c r="E92">
+        <v>206043.8</v>
+      </c>
+      <c r="F92" t="s">
+        <v>282</v>
+      </c>
+      <c r="H92" t="s">
+        <v>373</v>
+      </c>
+      <c r="J92" t="s">
+        <v>530</v>
+      </c>
+      <c r="K92" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93">
+        <v>914</v>
+      </c>
+      <c r="B93" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D93" t="s">
+        <v>241</v>
+      </c>
+      <c r="E93">
+        <v>300263.95</v>
+      </c>
+      <c r="H93" t="s">
+        <v>374</v>
+      </c>
+      <c r="J93" t="s">
+        <v>529</v>
+      </c>
+      <c r="K93" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94">
+        <v>923</v>
+      </c>
+      <c r="B94" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" t="s">
+        <v>133</v>
+      </c>
+      <c r="D94" t="s">
+        <v>241</v>
+      </c>
+      <c r="E94">
+        <v>305970.05</v>
+      </c>
+      <c r="I94" t="s">
+        <v>480</v>
+      </c>
+      <c r="J94" t="s">
+        <v>529</v>
+      </c>
+      <c r="K94" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95">
+        <v>931</v>
+      </c>
+      <c r="B95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" t="s">
+        <v>134</v>
+      </c>
+      <c r="D95" t="s">
+        <v>241</v>
+      </c>
+      <c r="E95">
+        <v>239959.86</v>
+      </c>
+      <c r="H95" t="s">
+        <v>375</v>
+      </c>
+      <c r="J95" t="s">
+        <v>529</v>
+      </c>
+      <c r="K95" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96">
+        <v>943</v>
+      </c>
+      <c r="B96" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" t="s">
+        <v>135</v>
+      </c>
+      <c r="D96" t="s">
+        <v>241</v>
+      </c>
+      <c r="E96">
+        <v>237646.53</v>
+      </c>
+      <c r="F96" t="s">
+        <v>283</v>
+      </c>
+      <c r="H96" t="s">
+        <v>376</v>
+      </c>
+      <c r="J96" t="s">
+        <v>530</v>
+      </c>
+      <c r="K96" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97">
+        <v>946</v>
+      </c>
+      <c r="B97" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>136</v>
+      </c>
+      <c r="D97" t="s">
+        <v>241</v>
+      </c>
+      <c r="E97">
+        <v>307832.24</v>
+      </c>
+      <c r="F97" t="s">
+        <v>284</v>
+      </c>
+      <c r="H97" t="s">
+        <v>377</v>
+      </c>
+      <c r="J97" t="s">
+        <v>530</v>
+      </c>
+      <c r="K97" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98">
+        <v>951</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>137</v>
+      </c>
+      <c r="D98" t="s">
+        <v>241</v>
+      </c>
+      <c r="E98">
+        <v>287163.32</v>
+      </c>
+      <c r="F98" t="s">
+        <v>285</v>
+      </c>
+      <c r="H98" t="s">
+        <v>378</v>
+      </c>
+      <c r="J98" t="s">
+        <v>530</v>
+      </c>
+      <c r="K98" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99">
+        <v>987</v>
+      </c>
+      <c r="B99" t="s">
+        <v>38</v>
+      </c>
+      <c r="C99" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" t="s">
+        <v>241</v>
+      </c>
+      <c r="E99">
+        <v>226036.69</v>
+      </c>
+      <c r="F99" t="s">
+        <v>286</v>
+      </c>
+      <c r="I99" t="s">
+        <v>481</v>
+      </c>
+      <c r="J99" t="s">
+        <v>530</v>
+      </c>
+      <c r="K99" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100">
+        <v>988</v>
+      </c>
+      <c r="B100" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" t="s">
+        <v>139</v>
+      </c>
+      <c r="D100" t="s">
+        <v>241</v>
+      </c>
+      <c r="E100">
+        <v>234711.45</v>
+      </c>
+      <c r="H100" t="s">
+        <v>379</v>
+      </c>
+      <c r="J100" t="s">
+        <v>529</v>
+      </c>
+      <c r="K100" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101">
+        <v>991</v>
+      </c>
+      <c r="B101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" t="s">
+        <v>140</v>
+      </c>
+      <c r="D101" t="s">
+        <v>241</v>
+      </c>
+      <c r="E101">
+        <v>256051.57</v>
+      </c>
+      <c r="F101" t="s">
+        <v>287</v>
+      </c>
+      <c r="I101" t="s">
+        <v>482</v>
+      </c>
+      <c r="J101" t="s">
+        <v>530</v>
+      </c>
+      <c r="K101" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102">
+        <v>995</v>
+      </c>
+      <c r="B102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102" t="s">
+        <v>141</v>
+      </c>
+      <c r="D102" t="s">
+        <v>241</v>
+      </c>
+      <c r="E102">
+        <v>239569.14</v>
+      </c>
+      <c r="H102" t="s">
+        <v>380</v>
+      </c>
+      <c r="J102" t="s">
+        <v>529</v>
+      </c>
+      <c r="K102" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103">
+        <v>999</v>
+      </c>
+      <c r="B103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103" t="s">
+        <v>142</v>
+      </c>
+      <c r="D103" t="s">
+        <v>241</v>
+      </c>
+      <c r="E103">
+        <v>257682.63</v>
+      </c>
+      <c r="F103" t="s">
+        <v>288</v>
+      </c>
+      <c r="H103" t="s">
+        <v>381</v>
+      </c>
+      <c r="J103" t="s">
+        <v>530</v>
+      </c>
+      <c r="K103" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104">
+        <v>1032</v>
+      </c>
+      <c r="B104" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104" t="s">
+        <v>143</v>
+      </c>
+      <c r="D104" t="s">
+        <v>241</v>
+      </c>
+      <c r="E104">
+        <v>307137.01</v>
+      </c>
+      <c r="F104" t="s">
+        <v>289</v>
+      </c>
+      <c r="H104" t="s">
+        <v>382</v>
+      </c>
+      <c r="J104" t="s">
+        <v>530</v>
+      </c>
+      <c r="K104" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105">
+        <v>1039</v>
+      </c>
+      <c r="B105" t="s">
+        <v>22</v>
+      </c>
+      <c r="C105" t="s">
+        <v>144</v>
+      </c>
+      <c r="D105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E105">
+        <v>232442.26</v>
+      </c>
+      <c r="F105" t="s">
+        <v>290</v>
+      </c>
+      <c r="I105" t="s">
+        <v>483</v>
+      </c>
+      <c r="J105" t="s">
+        <v>530</v>
+      </c>
+      <c r="K105" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106">
+        <v>1047</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>145</v>
+      </c>
+      <c r="D106" t="s">
+        <v>241</v>
+      </c>
+      <c r="E106">
+        <v>303629.77</v>
+      </c>
+      <c r="F106" t="s">
+        <v>291</v>
+      </c>
+      <c r="H106" t="s">
+        <v>383</v>
+      </c>
+      <c r="J106" t="s">
+        <v>530</v>
+      </c>
+      <c r="K106" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107">
+        <v>1075</v>
+      </c>
+      <c r="B107" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" t="s">
+        <v>146</v>
+      </c>
+      <c r="D107" t="s">
+        <v>241</v>
+      </c>
+      <c r="E107">
+        <v>249024.73</v>
+      </c>
+      <c r="F107" t="s">
+        <v>292</v>
+      </c>
+      <c r="H107" t="s">
+        <v>384</v>
+      </c>
+      <c r="J107" t="s">
+        <v>530</v>
+      </c>
+      <c r="K107" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108">
+        <v>1087</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" t="s">
+        <v>147</v>
+      </c>
+      <c r="D108" t="s">
+        <v>241</v>
+      </c>
+      <c r="E108">
+        <v>254522.79</v>
+      </c>
+      <c r="F108" t="s">
+        <v>293</v>
+      </c>
+      <c r="I108" t="s">
+        <v>484</v>
+      </c>
+      <c r="J108" t="s">
+        <v>530</v>
+      </c>
+      <c r="K108" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109">
+        <v>1113</v>
+      </c>
+      <c r="B109" t="s">
+        <v>28</v>
+      </c>
+      <c r="C109" t="s">
+        <v>148</v>
+      </c>
+      <c r="D109" t="s">
+        <v>241</v>
+      </c>
+      <c r="E109">
+        <v>274938.15</v>
+      </c>
+      <c r="F109" t="s">
+        <v>294</v>
+      </c>
+      <c r="I109" t="s">
+        <v>485</v>
+      </c>
+      <c r="J109" t="s">
+        <v>530</v>
+      </c>
+      <c r="K109" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110">
+        <v>1123</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" t="s">
+        <v>149</v>
+      </c>
+      <c r="D110" t="s">
+        <v>241</v>
+      </c>
+      <c r="E110">
+        <v>206997.13</v>
+      </c>
+      <c r="H110" t="s">
+        <v>385</v>
+      </c>
+      <c r="J110" t="s">
+        <v>529</v>
+      </c>
+      <c r="K110" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111">
+        <v>1126</v>
+      </c>
+      <c r="B111" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" t="s">
+        <v>150</v>
+      </c>
+      <c r="D111" t="s">
+        <v>241</v>
+      </c>
+      <c r="E111">
+        <v>217020.25</v>
+      </c>
+      <c r="I111" t="s">
+        <v>486</v>
+      </c>
+      <c r="J111" t="s">
+        <v>529</v>
+      </c>
+      <c r="K111" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112">
+        <v>1131</v>
+      </c>
+      <c r="B112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C112" t="s">
+        <v>151</v>
+      </c>
+      <c r="D112" t="s">
+        <v>241</v>
+      </c>
+      <c r="E112">
+        <v>283365.2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>295</v>
+      </c>
+      <c r="H112" t="s">
+        <v>386</v>
+      </c>
+      <c r="J112" t="s">
+        <v>530</v>
+      </c>
+      <c r="K112" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113">
+        <v>1133</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>152</v>
+      </c>
+      <c r="D113" t="s">
+        <v>241</v>
+      </c>
+      <c r="E113">
+        <v>240186.4</v>
+      </c>
+      <c r="I113" t="s">
+        <v>487</v>
+      </c>
+      <c r="J113" t="s">
+        <v>529</v>
+      </c>
+      <c r="K113" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114">
+        <v>1141</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>153</v>
+      </c>
+      <c r="D114" t="s">
+        <v>241</v>
+      </c>
+      <c r="E114">
+        <v>244045.44</v>
+      </c>
+      <c r="I114" t="s">
+        <v>488</v>
+      </c>
+      <c r="J114" t="s">
+        <v>529</v>
+      </c>
+      <c r="K114" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115">
+        <v>1151</v>
+      </c>
+      <c r="B115" t="s">
+        <v>39</v>
+      </c>
+      <c r="C115" t="s">
+        <v>154</v>
+      </c>
+      <c r="D115" t="s">
+        <v>241</v>
+      </c>
+      <c r="E115">
+        <v>275892.77</v>
+      </c>
+      <c r="H115" t="s">
+        <v>387</v>
+      </c>
+      <c r="J115" t="s">
+        <v>529</v>
+      </c>
+      <c r="K115" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116">
+        <v>1166</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>155</v>
+      </c>
+      <c r="D116" t="s">
+        <v>241</v>
+      </c>
+      <c r="E116">
+        <v>280567.01</v>
+      </c>
+      <c r="H116" t="s">
+        <v>388</v>
+      </c>
+      <c r="J116" t="s">
+        <v>529</v>
+      </c>
+      <c r="K116" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117">
+        <v>1172</v>
+      </c>
+      <c r="B117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C117" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" t="s">
+        <v>241</v>
+      </c>
+      <c r="E117">
+        <v>225319.64</v>
+      </c>
+      <c r="I117" t="s">
+        <v>489</v>
+      </c>
+      <c r="J117" t="s">
+        <v>529</v>
+      </c>
+      <c r="K117" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118">
+        <v>1185</v>
+      </c>
+      <c r="B118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" t="s">
+        <v>157</v>
+      </c>
+      <c r="D118" t="s">
+        <v>241</v>
+      </c>
+      <c r="E118">
+        <v>274087.43</v>
+      </c>
+      <c r="H118" t="s">
+        <v>389</v>
+      </c>
+      <c r="J118" t="s">
+        <v>529</v>
+      </c>
+      <c r="K118" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119">
+        <v>1191</v>
+      </c>
+      <c r="B119" t="s">
+        <v>35</v>
+      </c>
+      <c r="C119" t="s">
+        <v>158</v>
+      </c>
+      <c r="D119" t="s">
+        <v>241</v>
+      </c>
+      <c r="E119">
+        <v>274810.65</v>
+      </c>
+      <c r="I119" t="s">
+        <v>490</v>
+      </c>
+      <c r="J119" t="s">
+        <v>529</v>
+      </c>
+      <c r="K119" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120">
+        <v>1198</v>
+      </c>
+      <c r="B120" t="s">
+        <v>38</v>
+      </c>
+      <c r="C120" t="s">
+        <v>159</v>
+      </c>
+      <c r="D120" t="s">
+        <v>241</v>
+      </c>
+      <c r="E120">
+        <v>296414.2</v>
+      </c>
+      <c r="F120" t="s">
+        <v>296</v>
+      </c>
+      <c r="I120" t="s">
+        <v>491</v>
+      </c>
+      <c r="J120" t="s">
+        <v>530</v>
+      </c>
+      <c r="K120" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121">
+        <v>1203</v>
+      </c>
+      <c r="B121" t="s">
+        <v>28</v>
+      </c>
+      <c r="C121" t="s">
+        <v>160</v>
+      </c>
+      <c r="D121" t="s">
+        <v>241</v>
+      </c>
+      <c r="E121">
+        <v>281301.45</v>
+      </c>
+      <c r="H121" t="s">
+        <v>390</v>
+      </c>
+      <c r="J121" t="s">
+        <v>529</v>
+      </c>
+      <c r="K121" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122">
+        <v>1248</v>
+      </c>
+      <c r="B122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C122" t="s">
+        <v>161</v>
+      </c>
+      <c r="D122" t="s">
+        <v>241</v>
+      </c>
+      <c r="E122">
+        <v>248045.24</v>
+      </c>
+      <c r="F122" t="s">
+        <v>297</v>
+      </c>
+      <c r="I122" t="s">
+        <v>492</v>
+      </c>
+      <c r="J122" t="s">
+        <v>530</v>
+      </c>
+      <c r="K122" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123">
+        <v>1266</v>
+      </c>
+      <c r="B123" t="s">
+        <v>23</v>
+      </c>
+      <c r="C123" t="s">
+        <v>162</v>
+      </c>
+      <c r="D123" t="s">
+        <v>241</v>
+      </c>
+      <c r="E123">
+        <v>286638.47</v>
+      </c>
+      <c r="H123" t="s">
+        <v>391</v>
+      </c>
+      <c r="J123" t="s">
+        <v>529</v>
+      </c>
+      <c r="K123" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124">
+        <v>1268</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+      <c r="C124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" t="s">
+        <v>241</v>
+      </c>
+      <c r="E124">
+        <v>307225.19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>392</v>
+      </c>
+      <c r="J124" t="s">
+        <v>529</v>
+      </c>
+      <c r="K124" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125">
+        <v>1286</v>
+      </c>
+      <c r="B125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C125" t="s">
+        <v>164</v>
+      </c>
+      <c r="D125" t="s">
+        <v>241</v>
+      </c>
+      <c r="E125">
+        <v>268863.63</v>
+      </c>
+      <c r="F125" t="s">
+        <v>298</v>
+      </c>
+      <c r="H125" t="s">
+        <v>393</v>
+      </c>
+      <c r="J125" t="s">
+        <v>530</v>
+      </c>
+      <c r="K125" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126">
+        <v>1291</v>
+      </c>
+      <c r="B126" t="s">
+        <v>31</v>
+      </c>
+      <c r="C126" t="s">
+        <v>165</v>
+      </c>
+      <c r="D126" t="s">
+        <v>241</v>
+      </c>
+      <c r="E126">
+        <v>205240.8</v>
+      </c>
+      <c r="H126" t="s">
+        <v>394</v>
+      </c>
+      <c r="J126" t="s">
+        <v>529</v>
+      </c>
+      <c r="K126" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127">
+        <v>1293</v>
+      </c>
+      <c r="B127" t="s">
+        <v>23</v>
+      </c>
+      <c r="C127" t="s">
+        <v>166</v>
+      </c>
+      <c r="D127" t="s">
+        <v>241</v>
+      </c>
+      <c r="E127">
+        <v>287396.56</v>
+      </c>
+      <c r="I127" t="s">
+        <v>493</v>
+      </c>
+      <c r="J127" t="s">
+        <v>529</v>
+      </c>
+      <c r="K127" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128">
+        <v>1299</v>
+      </c>
+      <c r="B128" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" t="s">
+        <v>167</v>
+      </c>
+      <c r="D128" t="s">
+        <v>241</v>
+      </c>
+      <c r="E128">
+        <v>272626.97</v>
+      </c>
+      <c r="I128" t="s">
+        <v>494</v>
+      </c>
+      <c r="J128" t="s">
+        <v>529</v>
+      </c>
+      <c r="K128" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129">
+        <v>1301</v>
+      </c>
+      <c r="B129" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" t="s">
+        <v>168</v>
+      </c>
+      <c r="D129" t="s">
+        <v>241</v>
+      </c>
+      <c r="E129">
+        <v>261970.23</v>
+      </c>
+      <c r="F129" t="s">
+        <v>299</v>
+      </c>
+      <c r="H129" t="s">
+        <v>395</v>
+      </c>
+      <c r="J129" t="s">
+        <v>530</v>
+      </c>
+      <c r="K129" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130">
+        <v>1302</v>
+      </c>
+      <c r="B130" t="s">
+        <v>32</v>
+      </c>
+      <c r="C130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D130" t="s">
+        <v>241</v>
+      </c>
+      <c r="E130">
+        <v>302550.91</v>
+      </c>
+      <c r="I130" t="s">
+        <v>495</v>
+      </c>
+      <c r="J130" t="s">
+        <v>529</v>
+      </c>
+      <c r="K130" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131">
+        <v>1306</v>
+      </c>
+      <c r="B131" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D131" t="s">
+        <v>241</v>
+      </c>
+      <c r="E131">
+        <v>226796.75</v>
+      </c>
+      <c r="F131" t="s">
+        <v>300</v>
+      </c>
+      <c r="I131" t="s">
+        <v>496</v>
+      </c>
+      <c r="J131" t="s">
+        <v>530</v>
+      </c>
+      <c r="K131" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132">
+        <v>1307</v>
+      </c>
+      <c r="B132" t="s">
+        <v>28</v>
+      </c>
+      <c r="C132" t="s">
+        <v>171</v>
+      </c>
+      <c r="D132" t="s">
+        <v>241</v>
+      </c>
+      <c r="E132">
+        <v>301684.86</v>
+      </c>
+      <c r="H132" t="s">
+        <v>396</v>
+      </c>
+      <c r="J132" t="s">
+        <v>529</v>
+      </c>
+      <c r="K132" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133">
+        <v>1323</v>
+      </c>
+      <c r="B133" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" t="s">
+        <v>172</v>
+      </c>
+      <c r="D133" t="s">
+        <v>241</v>
+      </c>
+      <c r="E133">
+        <v>231858.59</v>
+      </c>
+      <c r="F133" t="s">
+        <v>301</v>
+      </c>
+      <c r="I133" t="s">
+        <v>497</v>
+      </c>
+      <c r="J133" t="s">
+        <v>530</v>
+      </c>
+      <c r="K133" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134">
+        <v>1326</v>
+      </c>
+      <c r="B134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C134" t="s">
+        <v>173</v>
+      </c>
+      <c r="D134" t="s">
+        <v>241</v>
+      </c>
+      <c r="E134">
+        <v>212502.24</v>
+      </c>
+      <c r="H134" t="s">
+        <v>397</v>
+      </c>
+      <c r="J134" t="s">
+        <v>529</v>
+      </c>
+      <c r="K134" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135">
+        <v>1333</v>
+      </c>
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135" t="s">
+        <v>174</v>
+      </c>
+      <c r="D135" t="s">
+        <v>241</v>
+      </c>
+      <c r="E135">
+        <v>220681.6</v>
+      </c>
+      <c r="F135" t="s">
+        <v>302</v>
+      </c>
+      <c r="H135" t="s">
+        <v>398</v>
+      </c>
+      <c r="J135" t="s">
+        <v>530</v>
+      </c>
+      <c r="K135" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136">
+        <v>1342</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" t="s">
+        <v>175</v>
+      </c>
+      <c r="D136" t="s">
+        <v>241</v>
+      </c>
+      <c r="E136">
+        <v>240569.78</v>
+      </c>
+      <c r="F136" t="s">
+        <v>303</v>
+      </c>
+      <c r="I136" t="s">
+        <v>498</v>
+      </c>
+      <c r="J136" t="s">
+        <v>530</v>
+      </c>
+      <c r="K136" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137">
+        <v>1354</v>
+      </c>
+      <c r="B137" t="s">
+        <v>20</v>
+      </c>
+      <c r="C137" t="s">
+        <v>176</v>
+      </c>
+      <c r="D137" t="s">
+        <v>241</v>
+      </c>
+      <c r="E137">
+        <v>296307.52</v>
+      </c>
+      <c r="H137" t="s">
+        <v>399</v>
+      </c>
+      <c r="J137" t="s">
+        <v>529</v>
+      </c>
+      <c r="K137" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138">
+        <v>1356</v>
+      </c>
+      <c r="B138" t="s">
+        <v>22</v>
+      </c>
+      <c r="C138" t="s">
+        <v>177</v>
+      </c>
+      <c r="D138" t="s">
+        <v>241</v>
+      </c>
+      <c r="E138">
+        <v>227934</v>
+      </c>
+      <c r="H138" t="s">
+        <v>400</v>
+      </c>
+      <c r="J138" t="s">
+        <v>529</v>
+      </c>
+      <c r="K138" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139">
+        <v>1364</v>
+      </c>
+      <c r="B139" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" t="s">
+        <v>178</v>
+      </c>
+      <c r="D139" t="s">
+        <v>241</v>
+      </c>
+      <c r="E139">
+        <v>265509.94</v>
+      </c>
+      <c r="F139" t="s">
+        <v>304</v>
+      </c>
+      <c r="H139" t="s">
+        <v>401</v>
+      </c>
+      <c r="J139" t="s">
+        <v>530</v>
+      </c>
+      <c r="K139" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140">
+        <v>1367</v>
+      </c>
+      <c r="B140" t="s">
+        <v>34</v>
+      </c>
+      <c r="C140" t="s">
+        <v>179</v>
+      </c>
+      <c r="D140" t="s">
+        <v>241</v>
+      </c>
+      <c r="E140">
+        <v>232083.14</v>
+      </c>
+      <c r="F140" t="s">
+        <v>305</v>
+      </c>
+      <c r="H140" t="s">
+        <v>402</v>
+      </c>
+      <c r="J140" t="s">
+        <v>530</v>
+      </c>
+      <c r="K140" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141">
+        <v>1376</v>
+      </c>
+      <c r="B141" t="s">
+        <v>37</v>
+      </c>
+      <c r="C141" t="s">
+        <v>180</v>
+      </c>
+      <c r="D141" t="s">
+        <v>241</v>
+      </c>
+      <c r="E141">
+        <v>279017.57</v>
+      </c>
+      <c r="I141" t="s">
+        <v>499</v>
+      </c>
+      <c r="J141" t="s">
+        <v>529</v>
+      </c>
+      <c r="K141" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142">
+        <v>1386</v>
+      </c>
+      <c r="B142" t="s">
+        <v>39</v>
+      </c>
+      <c r="C142" t="s">
+        <v>181</v>
+      </c>
+      <c r="D142" t="s">
+        <v>241</v>
+      </c>
+      <c r="E142">
+        <v>226535.71</v>
+      </c>
+      <c r="F142" t="s">
+        <v>306</v>
+      </c>
+      <c r="H142" t="s">
+        <v>403</v>
+      </c>
+      <c r="J142" t="s">
+        <v>530</v>
+      </c>
+      <c r="K142" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143">
+        <v>1387</v>
+      </c>
+      <c r="B143" t="s">
+        <v>34</v>
+      </c>
+      <c r="C143" t="s">
+        <v>182</v>
+      </c>
+      <c r="D143" t="s">
+        <v>241</v>
+      </c>
+      <c r="E143">
+        <v>237938.83</v>
+      </c>
+      <c r="H143" t="s">
+        <v>404</v>
+      </c>
+      <c r="J143" t="s">
+        <v>529</v>
+      </c>
+      <c r="K143" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144">
+        <v>1397</v>
+      </c>
+      <c r="B144" t="s">
+        <v>18</v>
+      </c>
+      <c r="C144" t="s">
+        <v>183</v>
+      </c>
+      <c r="D144" t="s">
+        <v>241</v>
+      </c>
+      <c r="E144">
+        <v>292204.7</v>
+      </c>
+      <c r="F144" t="s">
+        <v>307</v>
+      </c>
+      <c r="H144" t="s">
+        <v>405</v>
+      </c>
+      <c r="J144" t="s">
+        <v>530</v>
+      </c>
+      <c r="K144" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145">
+        <v>1420</v>
+      </c>
+      <c r="B145" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145" t="s">
+        <v>184</v>
+      </c>
+      <c r="D145" t="s">
+        <v>241</v>
+      </c>
+      <c r="E145">
+        <v>214552.22</v>
+      </c>
+      <c r="I145" t="s">
+        <v>500</v>
+      </c>
+      <c r="J145" t="s">
+        <v>529</v>
+      </c>
+      <c r="K145" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146">
+        <v>1449</v>
+      </c>
+      <c r="B146" t="s">
+        <v>23</v>
+      </c>
+      <c r="C146" t="s">
+        <v>185</v>
+      </c>
+      <c r="D146" t="s">
+        <v>241</v>
+      </c>
+      <c r="E146">
+        <v>251463.81</v>
+      </c>
+      <c r="H146" t="s">
+        <v>406</v>
+      </c>
+      <c r="J146" t="s">
+        <v>529</v>
+      </c>
+      <c r="K146" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147">
+        <v>1475</v>
+      </c>
+      <c r="B147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C147" t="s">
+        <v>186</v>
+      </c>
+      <c r="D147" t="s">
+        <v>241</v>
+      </c>
+      <c r="E147">
+        <v>202880.17</v>
+      </c>
+      <c r="F147" t="s">
+        <v>308</v>
+      </c>
+      <c r="H147" t="s">
+        <v>407</v>
+      </c>
+      <c r="J147" t="s">
+        <v>530</v>
+      </c>
+      <c r="K147" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148">
+        <v>1497</v>
+      </c>
+      <c r="B148" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" t="s">
+        <v>187</v>
+      </c>
+      <c r="D148" t="s">
+        <v>241</v>
+      </c>
+      <c r="E148">
+        <v>241368.08</v>
+      </c>
+      <c r="I148" t="s">
+        <v>501</v>
+      </c>
+      <c r="J148" t="s">
+        <v>529</v>
+      </c>
+      <c r="K148" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149">
+        <v>1512</v>
+      </c>
+      <c r="B149" t="s">
+        <v>36</v>
+      </c>
+      <c r="C149" t="s">
+        <v>188</v>
+      </c>
+      <c r="D149" t="s">
+        <v>241</v>
+      </c>
+      <c r="E149">
+        <v>254285.41</v>
+      </c>
+      <c r="H149" t="s">
+        <v>408</v>
+      </c>
+      <c r="J149" t="s">
+        <v>529</v>
+      </c>
+      <c r="K149" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150">
+        <v>1513</v>
+      </c>
+      <c r="B150" t="s">
+        <v>39</v>
+      </c>
+      <c r="C150" t="s">
+        <v>189</v>
+      </c>
+      <c r="D150" t="s">
+        <v>241</v>
+      </c>
+      <c r="E150">
+        <v>236385.49</v>
+      </c>
+      <c r="F150" t="s">
+        <v>309</v>
+      </c>
+      <c r="H150" t="s">
+        <v>409</v>
+      </c>
+      <c r="J150" t="s">
+        <v>530</v>
+      </c>
+      <c r="K150" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151">
+        <v>1528</v>
+      </c>
+      <c r="B151" t="s">
+        <v>34</v>
+      </c>
+      <c r="C151" t="s">
+        <v>190</v>
+      </c>
+      <c r="D151" t="s">
+        <v>241</v>
+      </c>
+      <c r="E151">
+        <v>200987.54</v>
+      </c>
+      <c r="I151" t="s">
+        <v>502</v>
+      </c>
+      <c r="J151" t="s">
+        <v>529</v>
+      </c>
+      <c r="K151" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152">
+        <v>1535</v>
+      </c>
+      <c r="B152" t="s">
+        <v>27</v>
+      </c>
+      <c r="C152" t="s">
+        <v>191</v>
+      </c>
+      <c r="D152" t="s">
+        <v>241</v>
+      </c>
+      <c r="E152">
+        <v>216826.2</v>
+      </c>
+      <c r="I152" t="s">
+        <v>503</v>
+      </c>
+      <c r="J152" t="s">
+        <v>529</v>
+      </c>
+      <c r="K152" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153">
+        <v>1539</v>
+      </c>
+      <c r="B153" t="s">
+        <v>33</v>
+      </c>
+      <c r="C153" t="s">
+        <v>192</v>
+      </c>
+      <c r="D153" t="s">
+        <v>241</v>
+      </c>
+      <c r="E153">
+        <v>303752.04</v>
+      </c>
+      <c r="H153" t="s">
+        <v>410</v>
+      </c>
+      <c r="J153" t="s">
+        <v>529</v>
+      </c>
+      <c r="K153" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154">
+        <v>1543</v>
+      </c>
+      <c r="B154" t="s">
+        <v>18</v>
+      </c>
+      <c r="C154" t="s">
+        <v>193</v>
+      </c>
+      <c r="D154" t="s">
+        <v>241</v>
+      </c>
+      <c r="E154">
+        <v>258612.86</v>
+      </c>
+      <c r="H154" t="s">
+        <v>411</v>
+      </c>
+      <c r="J154" t="s">
+        <v>529</v>
+      </c>
+      <c r="K154" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155">
+        <v>1556</v>
+      </c>
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" t="s">
+        <v>194</v>
+      </c>
+      <c r="D155" t="s">
+        <v>241</v>
+      </c>
+      <c r="E155">
+        <v>278559.95</v>
+      </c>
+      <c r="I155" t="s">
+        <v>504</v>
+      </c>
+      <c r="J155" t="s">
+        <v>529</v>
+      </c>
+      <c r="K155" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156">
+        <v>1559</v>
+      </c>
+      <c r="B156" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" t="s">
+        <v>195</v>
+      </c>
+      <c r="D156" t="s">
+        <v>241</v>
+      </c>
+      <c r="E156">
+        <v>206181.3</v>
+      </c>
+      <c r="I156" t="s">
+        <v>505</v>
+      </c>
+      <c r="J156" t="s">
+        <v>529</v>
+      </c>
+      <c r="K156" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="A157">
+        <v>1561</v>
+      </c>
+      <c r="B157" t="s">
+        <v>37</v>
+      </c>
+      <c r="C157" t="s">
+        <v>196</v>
+      </c>
+      <c r="D157" t="s">
+        <v>241</v>
+      </c>
+      <c r="E157">
+        <v>274701.29</v>
+      </c>
+      <c r="I157" t="s">
+        <v>506</v>
+      </c>
+      <c r="J157" t="s">
+        <v>529</v>
+      </c>
+      <c r="K157" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="A158">
+        <v>1563</v>
+      </c>
+      <c r="B158" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158" t="s">
+        <v>197</v>
+      </c>
+      <c r="D158" t="s">
+        <v>241</v>
+      </c>
+      <c r="E158">
+        <v>255576.6</v>
+      </c>
+      <c r="F158" t="s">
+        <v>310</v>
+      </c>
+      <c r="H158" t="s">
+        <v>412</v>
+      </c>
+      <c r="J158" t="s">
+        <v>530</v>
+      </c>
+      <c r="K158" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="A159">
+        <v>1564</v>
+      </c>
+      <c r="B159" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" t="s">
+        <v>198</v>
+      </c>
+      <c r="D159" t="s">
+        <v>241</v>
+      </c>
+      <c r="E159">
+        <v>308045.62</v>
+      </c>
+      <c r="F159" t="s">
+        <v>311</v>
+      </c>
+      <c r="H159" t="s">
+        <v>413</v>
+      </c>
+      <c r="J159" t="s">
+        <v>530</v>
+      </c>
+      <c r="K159" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="A160">
+        <v>1576</v>
+      </c>
+      <c r="B160" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" t="s">
+        <v>199</v>
+      </c>
+      <c r="D160" t="s">
+        <v>241</v>
+      </c>
+      <c r="E160">
+        <v>305624.3</v>
+      </c>
+      <c r="F160" t="s">
+        <v>312</v>
+      </c>
+      <c r="H160" t="s">
+        <v>414</v>
+      </c>
+      <c r="J160" t="s">
+        <v>530</v>
+      </c>
+      <c r="K160" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="A161">
+        <v>1577</v>
+      </c>
+      <c r="B161" t="s">
+        <v>28</v>
+      </c>
+      <c r="C161" t="s">
+        <v>200</v>
+      </c>
+      <c r="D161" t="s">
+        <v>241</v>
+      </c>
+      <c r="E161">
+        <v>252451.43</v>
+      </c>
+      <c r="H161" t="s">
+        <v>415</v>
+      </c>
+      <c r="J161" t="s">
+        <v>529</v>
+      </c>
+      <c r="K161" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="A162">
+        <v>1585</v>
+      </c>
+      <c r="B162" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" t="s">
+        <v>201</v>
+      </c>
+      <c r="D162" t="s">
+        <v>241</v>
+      </c>
+      <c r="E162">
+        <v>233010.72</v>
+      </c>
+      <c r="H162" t="s">
+        <v>416</v>
+      </c>
+      <c r="J162" t="s">
+        <v>529</v>
+      </c>
+      <c r="K162" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="A163">
+        <v>1604</v>
+      </c>
+      <c r="B163" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" t="s">
+        <v>202</v>
+      </c>
+      <c r="D163" t="s">
+        <v>241</v>
+      </c>
+      <c r="E163">
+        <v>264777.41</v>
+      </c>
+      <c r="H163" t="s">
+        <v>417</v>
+      </c>
+      <c r="J163" t="s">
+        <v>529</v>
+      </c>
+      <c r="K163" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164">
+        <v>1642</v>
+      </c>
+      <c r="B164" t="s">
+        <v>33</v>
+      </c>
+      <c r="C164" t="s">
+        <v>203</v>
+      </c>
+      <c r="D164" t="s">
+        <v>241</v>
+      </c>
+      <c r="E164">
+        <v>218722.71</v>
+      </c>
+      <c r="F164" t="s">
+        <v>313</v>
+      </c>
+      <c r="H164" t="s">
+        <v>418</v>
+      </c>
+      <c r="J164" t="s">
+        <v>530</v>
+      </c>
+      <c r="K164" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="A165">
+        <v>1644</v>
+      </c>
+      <c r="B165" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" t="s">
+        <v>204</v>
+      </c>
+      <c r="D165" t="s">
+        <v>241</v>
+      </c>
+      <c r="E165">
+        <v>250395.74</v>
+      </c>
+      <c r="H165" t="s">
+        <v>419</v>
+      </c>
+      <c r="J165" t="s">
+        <v>529</v>
+      </c>
+      <c r="K165" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166">
+        <v>1649</v>
+      </c>
+      <c r="B166" t="s">
+        <v>33</v>
+      </c>
+      <c r="C166" t="s">
+        <v>205</v>
+      </c>
+      <c r="D166" t="s">
+        <v>241</v>
+      </c>
+      <c r="E166">
+        <v>246269.69</v>
+      </c>
+      <c r="I166" t="s">
+        <v>507</v>
+      </c>
+      <c r="J166" t="s">
+        <v>529</v>
+      </c>
+      <c r="K166" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="A167">
+        <v>1654</v>
+      </c>
+      <c r="B167" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" t="s">
+        <v>206</v>
+      </c>
+      <c r="D167" t="s">
+        <v>241</v>
+      </c>
+      <c r="E167">
+        <v>266757.63</v>
+      </c>
+      <c r="F167" t="s">
+        <v>314</v>
+      </c>
+      <c r="I167" t="s">
+        <v>508</v>
+      </c>
+      <c r="J167" t="s">
+        <v>530</v>
+      </c>
+      <c r="K167" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="A168">
+        <v>1662</v>
+      </c>
+      <c r="B168" t="s">
+        <v>38</v>
+      </c>
+      <c r="C168" t="s">
+        <v>207</v>
+      </c>
+      <c r="D168" t="s">
+        <v>241</v>
+      </c>
+      <c r="E168">
+        <v>305403.3</v>
+      </c>
+      <c r="H168" t="s">
+        <v>420</v>
+      </c>
+      <c r="J168" t="s">
+        <v>529</v>
+      </c>
+      <c r="K168" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169">
+        <v>1708</v>
+      </c>
+      <c r="B169" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" t="s">
+        <v>208</v>
+      </c>
+      <c r="D169" t="s">
+        <v>241</v>
+      </c>
+      <c r="E169">
+        <v>235635.12</v>
+      </c>
+      <c r="I169" t="s">
+        <v>509</v>
+      </c>
+      <c r="J169" t="s">
+        <v>529</v>
+      </c>
+      <c r="K169" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170">
+        <v>1724</v>
+      </c>
+      <c r="B170" t="s">
+        <v>26</v>
+      </c>
+      <c r="C170" t="s">
+        <v>209</v>
+      </c>
+      <c r="D170" t="s">
+        <v>241</v>
+      </c>
+      <c r="E170">
+        <v>260882.36</v>
+      </c>
+      <c r="I170" t="s">
+        <v>510</v>
+      </c>
+      <c r="J170" t="s">
+        <v>529</v>
+      </c>
+      <c r="K170" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171">
+        <v>1729</v>
+      </c>
+      <c r="B171" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" t="s">
+        <v>210</v>
+      </c>
+      <c r="D171" t="s">
+        <v>241</v>
+      </c>
+      <c r="E171">
+        <v>203596.51</v>
+      </c>
+      <c r="H171" t="s">
+        <v>421</v>
+      </c>
+      <c r="J171" t="s">
+        <v>529</v>
+      </c>
+      <c r="K171" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172">
+        <v>1749</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" t="s">
+        <v>211</v>
+      </c>
+      <c r="D172" t="s">
+        <v>241</v>
+      </c>
+      <c r="E172">
+        <v>283990.89</v>
+      </c>
+      <c r="I172" t="s">
+        <v>511</v>
+      </c>
+      <c r="J172" t="s">
+        <v>529</v>
+      </c>
+      <c r="K172" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173">
+        <v>1785</v>
+      </c>
+      <c r="B173" t="s">
+        <v>33</v>
+      </c>
+      <c r="C173" t="s">
+        <v>212</v>
+      </c>
+      <c r="D173" t="s">
+        <v>241</v>
+      </c>
+      <c r="E173">
+        <v>288456.48</v>
+      </c>
+      <c r="I173" t="s">
+        <v>512</v>
+      </c>
+      <c r="J173" t="s">
+        <v>529</v>
+      </c>
+      <c r="K173" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174">
+        <v>1791</v>
+      </c>
+      <c r="B174" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" t="s">
+        <v>213</v>
+      </c>
+      <c r="D174" t="s">
+        <v>241</v>
+      </c>
+      <c r="E174">
+        <v>259344.35</v>
+      </c>
+      <c r="F174" t="s">
+        <v>315</v>
+      </c>
+      <c r="I174" t="s">
+        <v>513</v>
+      </c>
+      <c r="J174" t="s">
+        <v>530</v>
+      </c>
+      <c r="K174" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175">
+        <v>1801</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" t="s">
+        <v>214</v>
+      </c>
+      <c r="D175" t="s">
+        <v>241</v>
+      </c>
+      <c r="E175">
+        <v>212823.6</v>
+      </c>
+      <c r="F175" t="s">
+        <v>316</v>
+      </c>
+      <c r="I175" t="s">
+        <v>514</v>
+      </c>
+      <c r="J175" t="s">
+        <v>530</v>
+      </c>
+      <c r="K175" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176">
+        <v>1803</v>
+      </c>
+      <c r="B176" t="s">
+        <v>35</v>
+      </c>
+      <c r="C176" t="s">
+        <v>215</v>
+      </c>
+      <c r="D176" t="s">
+        <v>241</v>
+      </c>
+      <c r="E176">
+        <v>261973.07</v>
+      </c>
+      <c r="I176" t="s">
+        <v>515</v>
+      </c>
+      <c r="J176" t="s">
+        <v>529</v>
+      </c>
+      <c r="K176" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177">
+        <v>1805</v>
+      </c>
+      <c r="B177" t="s">
+        <v>30</v>
+      </c>
+      <c r="C177" t="s">
+        <v>216</v>
+      </c>
+      <c r="D177" t="s">
+        <v>241</v>
+      </c>
+      <c r="E177">
+        <v>209304.75</v>
+      </c>
+      <c r="F177" t="s">
+        <v>317</v>
+      </c>
+      <c r="H177" t="s">
+        <v>422</v>
+      </c>
+      <c r="J177" t="s">
+        <v>530</v>
+      </c>
+      <c r="K177" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178">
+        <v>1829</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" t="s">
+        <v>217</v>
+      </c>
+      <c r="D178" t="s">
+        <v>241</v>
+      </c>
+      <c r="E178">
+        <v>245122.52</v>
+      </c>
+      <c r="I178" t="s">
+        <v>516</v>
+      </c>
+      <c r="J178" t="s">
+        <v>529</v>
+      </c>
+      <c r="K178" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179">
+        <v>1837</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179" t="s">
+        <v>218</v>
+      </c>
+      <c r="D179" t="s">
+        <v>241</v>
+      </c>
+      <c r="E179">
+        <v>222267.77</v>
+      </c>
+      <c r="H179" t="s">
+        <v>423</v>
+      </c>
+      <c r="J179" t="s">
+        <v>529</v>
+      </c>
+      <c r="K179" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180">
+        <v>1843</v>
+      </c>
+      <c r="B180" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" t="s">
+        <v>219</v>
+      </c>
+      <c r="D180" t="s">
+        <v>241</v>
+      </c>
+      <c r="E180">
+        <v>263473.55</v>
+      </c>
+      <c r="H180" t="s">
+        <v>424</v>
+      </c>
+      <c r="J180" t="s">
+        <v>529</v>
+      </c>
+      <c r="K180" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181">
+        <v>1850</v>
+      </c>
+      <c r="B181" t="s">
+        <v>22</v>
+      </c>
+      <c r="C181" t="s">
+        <v>220</v>
+      </c>
+      <c r="D181" t="s">
+        <v>241</v>
+      </c>
+      <c r="E181">
+        <v>244819.06</v>
+      </c>
+      <c r="F181" t="s">
+        <v>318</v>
+      </c>
+      <c r="H181" t="s">
+        <v>425</v>
+      </c>
+      <c r="J181" t="s">
+        <v>530</v>
+      </c>
+      <c r="K181" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182">
+        <v>1852</v>
+      </c>
+      <c r="B182" t="s">
+        <v>31</v>
+      </c>
+      <c r="C182" t="s">
+        <v>221</v>
+      </c>
+      <c r="D182" t="s">
+        <v>241</v>
+      </c>
+      <c r="E182">
+        <v>260189.58</v>
+      </c>
+      <c r="H182" t="s">
+        <v>426</v>
+      </c>
+      <c r="J182" t="s">
+        <v>529</v>
+      </c>
+      <c r="K182" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="A183">
+        <v>1860</v>
+      </c>
+      <c r="B183" t="s">
+        <v>40</v>
+      </c>
+      <c r="C183" t="s">
+        <v>222</v>
+      </c>
+      <c r="D183" t="s">
+        <v>241</v>
+      </c>
+      <c r="E183">
+        <v>299671.36</v>
+      </c>
+      <c r="I183" t="s">
+        <v>517</v>
+      </c>
+      <c r="J183" t="s">
+        <v>529</v>
+      </c>
+      <c r="K183" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="A184">
+        <v>1872</v>
+      </c>
+      <c r="B184" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" t="s">
+        <v>223</v>
+      </c>
+      <c r="D184" t="s">
+        <v>241</v>
+      </c>
+      <c r="E184">
+        <v>278267.62</v>
+      </c>
+      <c r="F184" t="s">
+        <v>319</v>
+      </c>
+      <c r="I184" t="s">
+        <v>518</v>
+      </c>
+      <c r="J184" t="s">
+        <v>530</v>
+      </c>
+      <c r="K184" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
+      <c r="A185">
+        <v>1877</v>
+      </c>
+      <c r="B185" t="s">
+        <v>12</v>
+      </c>
+      <c r="C185" t="s">
+        <v>224</v>
+      </c>
+      <c r="D185" t="s">
+        <v>241</v>
+      </c>
+      <c r="E185">
+        <v>202197.75</v>
+      </c>
+      <c r="I185" t="s">
+        <v>519</v>
+      </c>
+      <c r="J185" t="s">
+        <v>529</v>
+      </c>
+      <c r="K185" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
+      <c r="A186">
+        <v>1879</v>
+      </c>
+      <c r="B186" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" t="s">
+        <v>225</v>
+      </c>
+      <c r="D186" t="s">
+        <v>241</v>
+      </c>
+      <c r="E186">
+        <v>260695.38</v>
+      </c>
+      <c r="F186" t="s">
+        <v>320</v>
+      </c>
+      <c r="H186" t="s">
+        <v>427</v>
+      </c>
+      <c r="J186" t="s">
+        <v>530</v>
+      </c>
+      <c r="K186" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187">
+        <v>1928</v>
+      </c>
+      <c r="B187" t="s">
+        <v>21</v>
+      </c>
+      <c r="C187" t="s">
+        <v>226</v>
+      </c>
+      <c r="D187" t="s">
+        <v>241</v>
+      </c>
+      <c r="E187">
+        <v>284325.94</v>
+      </c>
+      <c r="H187" t="s">
+        <v>428</v>
+      </c>
+      <c r="J187" t="s">
+        <v>529</v>
+      </c>
+      <c r="K187" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
+      <c r="A188">
+        <v>1937</v>
+      </c>
+      <c r="B188" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188" t="s">
+        <v>227</v>
+      </c>
+      <c r="D188" t="s">
+        <v>241</v>
+      </c>
+      <c r="E188">
+        <v>251561.8</v>
+      </c>
+      <c r="F188" t="s">
+        <v>321</v>
+      </c>
+      <c r="I188" t="s">
+        <v>520</v>
+      </c>
+      <c r="J188" t="s">
+        <v>530</v>
+      </c>
+      <c r="K188" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189">
+        <v>1963</v>
+      </c>
+      <c r="B189" t="s">
+        <v>28</v>
+      </c>
+      <c r="C189" t="s">
+        <v>228</v>
+      </c>
+      <c r="D189" t="s">
+        <v>241</v>
+      </c>
+      <c r="E189">
+        <v>245796.85</v>
+      </c>
+      <c r="I189" t="s">
+        <v>521</v>
+      </c>
+      <c r="J189" t="s">
+        <v>529</v>
+      </c>
+      <c r="K189" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
+      <c r="A190">
+        <v>1968</v>
+      </c>
+      <c r="B190" t="s">
+        <v>40</v>
+      </c>
+      <c r="C190" t="s">
+        <v>229</v>
+      </c>
+      <c r="D190" t="s">
+        <v>241</v>
+      </c>
+      <c r="E190">
+        <v>218817.54</v>
+      </c>
+      <c r="I190" t="s">
+        <v>522</v>
+      </c>
+      <c r="J190" t="s">
+        <v>529</v>
+      </c>
+      <c r="K190" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
+      <c r="A191">
+        <v>1982</v>
+      </c>
+      <c r="B191" t="s">
+        <v>37</v>
+      </c>
+      <c r="C191" t="s">
+        <v>230</v>
+      </c>
+      <c r="D191" t="s">
+        <v>241</v>
+      </c>
+      <c r="E191">
+        <v>259501.63</v>
+      </c>
+      <c r="H191" t="s">
+        <v>429</v>
+      </c>
+      <c r="J191" t="s">
+        <v>529</v>
+      </c>
+      <c r="K191" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
+      <c r="A192">
+        <v>1992</v>
+      </c>
+      <c r="B192" t="s">
+        <v>14</v>
+      </c>
+      <c r="C192" t="s">
+        <v>231</v>
+      </c>
+      <c r="D192" t="s">
+        <v>241</v>
+      </c>
+      <c r="E192">
+        <v>233537.69</v>
+      </c>
+      <c r="F192" t="s">
+        <v>322</v>
+      </c>
+      <c r="I192" t="s">
+        <v>523</v>
+      </c>
+      <c r="J192" t="s">
+        <v>530</v>
+      </c>
+      <c r="K192" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
+      <c r="A193">
+        <v>1996</v>
+      </c>
+      <c r="B193" t="s">
+        <v>21</v>
+      </c>
+      <c r="C193" t="s">
+        <v>232</v>
+      </c>
+      <c r="D193" t="s">
+        <v>241</v>
+      </c>
+      <c r="E193">
+        <v>252003.27</v>
+      </c>
+      <c r="I193" t="s">
+        <v>524</v>
+      </c>
+      <c r="J193" t="s">
+        <v>529</v>
+      </c>
+      <c r="K193" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
+      <c r="A194">
+        <v>2001</v>
+      </c>
+      <c r="B194" t="s">
+        <v>37</v>
+      </c>
+      <c r="C194" t="s">
+        <v>233</v>
+      </c>
+      <c r="D194" t="s">
+        <v>241</v>
+      </c>
+      <c r="E194">
+        <v>214961.5</v>
+      </c>
+      <c r="F194" t="s">
+        <v>323</v>
+      </c>
+      <c r="I194" t="s">
+        <v>525</v>
+      </c>
+      <c r="J194" t="s">
+        <v>530</v>
+      </c>
+      <c r="K194" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
+      <c r="A195">
+        <v>2030</v>
+      </c>
+      <c r="B195" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" t="s">
+        <v>234</v>
+      </c>
+      <c r="D195" t="s">
+        <v>241</v>
+      </c>
+      <c r="E195">
+        <v>228294.84</v>
+      </c>
+      <c r="H195" t="s">
+        <v>430</v>
+      </c>
+      <c r="J195" t="s">
+        <v>529</v>
+      </c>
+      <c r="K195" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
+      <c r="A196">
+        <v>2037</v>
+      </c>
+      <c r="B196" t="s">
+        <v>38</v>
+      </c>
+      <c r="C196" t="s">
+        <v>235</v>
+      </c>
+      <c r="D196" t="s">
+        <v>241</v>
+      </c>
+      <c r="E196">
+        <v>227993.89</v>
+      </c>
+      <c r="F196" t="s">
+        <v>324</v>
+      </c>
+      <c r="H196" t="s">
+        <v>431</v>
+      </c>
+      <c r="J196" t="s">
+        <v>530</v>
+      </c>
+      <c r="K196" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
+      <c r="A197">
+        <v>2049</v>
+      </c>
+      <c r="B197" t="s">
+        <v>40</v>
+      </c>
+      <c r="C197" t="s">
+        <v>236</v>
+      </c>
+      <c r="D197" t="s">
+        <v>241</v>
+      </c>
+      <c r="E197">
+        <v>223198.35</v>
+      </c>
+      <c r="F197" t="s">
+        <v>325</v>
+      </c>
+      <c r="I197" t="s">
+        <v>526</v>
+      </c>
+      <c r="J197" t="s">
+        <v>530</v>
+      </c>
+      <c r="K197" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
+      <c r="A198">
+        <v>2084</v>
+      </c>
+      <c r="B198" t="s">
+        <v>33</v>
+      </c>
+      <c r="C198" t="s">
+        <v>237</v>
+      </c>
+      <c r="D198" t="s">
+        <v>241</v>
+      </c>
+      <c r="E198">
+        <v>298030.41</v>
+      </c>
+      <c r="H198" t="s">
+        <v>432</v>
+      </c>
+      <c r="J198" t="s">
+        <v>529</v>
+      </c>
+      <c r="K198" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
+      <c r="A199">
+        <v>2105</v>
+      </c>
+      <c r="B199" t="s">
+        <v>30</v>
+      </c>
+      <c r="C199" t="s">
+        <v>238</v>
+      </c>
+      <c r="D199" t="s">
+        <v>241</v>
+      </c>
+      <c r="E199">
+        <v>280262.17</v>
+      </c>
+      <c r="F199" t="s">
+        <v>326</v>
+      </c>
+      <c r="I199" t="s">
+        <v>527</v>
+      </c>
+      <c r="J199" t="s">
+        <v>530</v>
+      </c>
+      <c r="K199" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200">
+        <v>2114</v>
+      </c>
+      <c r="B200" t="s">
+        <v>23</v>
+      </c>
+      <c r="C200" t="s">
+        <v>239</v>
+      </c>
+      <c r="D200" t="s">
+        <v>241</v>
+      </c>
+      <c r="E200">
+        <v>297542.27</v>
+      </c>
+      <c r="F200" t="s">
+        <v>327</v>
+      </c>
+      <c r="H200" t="s">
+        <v>433</v>
+      </c>
+      <c r="J200" t="s">
+        <v>530</v>
+      </c>
+      <c r="K200" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201">
+        <v>2129</v>
+      </c>
+      <c r="B201" t="s">
+        <v>33</v>
+      </c>
+      <c r="C201" t="s">
+        <v>240</v>
+      </c>
+      <c r="D201" t="s">
+        <v>241</v>
+      </c>
+      <c r="E201">
+        <v>258431.27</v>
+      </c>
+      <c r="F201" t="s">
+        <v>328</v>
+      </c>
+      <c r="I201" t="s">
+        <v>528</v>
+      </c>
+      <c r="J201" t="s">
+        <v>530</v>
+      </c>
+      <c r="K201" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>

--- a/python-service/pan_issue_rows_debug.xlsx
+++ b/python-service/pan_issue_rows_debug.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="86">
   <si>
     <t>rowNumber</t>
   </si>
@@ -49,22 +49,229 @@
     <t>messages</t>
   </si>
   <si>
+    <t>02-04-2025</t>
+  </si>
+  <si>
     <t>03-04-2025</t>
   </si>
   <si>
-    <t>JH/B/2526/1</t>
+    <t>05-04-2025</t>
+  </si>
+  <si>
+    <t>09-04-2025</t>
+  </si>
+  <si>
+    <t>10-04-2025</t>
+  </si>
+  <si>
+    <t>15-04-2025</t>
+  </si>
+  <si>
+    <t>17-04-2025</t>
+  </si>
+  <si>
+    <t>18-04-2025</t>
+  </si>
+  <si>
+    <t>21-04-2025</t>
+  </si>
+  <si>
+    <t>25-04-2025</t>
+  </si>
+  <si>
+    <t>27-04-2025</t>
+  </si>
+  <si>
+    <t>28-04-2025</t>
+  </si>
+  <si>
+    <t>29-04-2025</t>
+  </si>
+  <si>
+    <t>JH/2526/ 15</t>
+  </si>
+  <si>
+    <t>JH/2526/ 18</t>
+  </si>
+  <si>
+    <t>JH/2526/ 66</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 1</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 2</t>
+  </si>
+  <si>
+    <t>JH/2526/ 120</t>
+  </si>
+  <si>
+    <t>JH/2526/ 275</t>
+  </si>
+  <si>
+    <t>JH/2526/ 278</t>
+  </si>
+  <si>
+    <t>JH/2526/ 321</t>
+  </si>
+  <si>
+    <t>JH/2526/ 329</t>
+  </si>
+  <si>
+    <t>JH/2526/ 480</t>
+  </si>
+  <si>
+    <t>JH/2526/ 645</t>
+  </si>
+  <si>
+    <t>JH/2526/ 681</t>
+  </si>
+  <si>
+    <t>JH/2526/ 683</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 3</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 4</t>
+  </si>
+  <si>
+    <t>JH/2526/ 910</t>
+  </si>
+  <si>
+    <t>JH/2526/ 939</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 5</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 7</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 8</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 9</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 13</t>
+  </si>
+  <si>
+    <t>JH/B/2526/ 14</t>
+  </si>
+  <si>
+    <t>Mrs. Tanuja Vemuri Bandi</t>
+  </si>
+  <si>
+    <t>Mrs. Revathi Krushi Duggirala</t>
+  </si>
+  <si>
+    <t>Mrs. Srilakshmi Veeramachineni</t>
   </si>
   <si>
     <t>Kundan Crafts Private Limited</t>
   </si>
   <si>
-    <t>Doc</t>
+    <t>House of B N M Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Ram Sunder R Kadari</t>
+  </si>
+  <si>
+    <t>Mrs. Krishna Varshitha Kotha,</t>
+  </si>
+  <si>
+    <t>Mrs. Varija Koppu,</t>
+  </si>
+  <si>
+    <t>Mrs. Sarvani Manne,</t>
+  </si>
+  <si>
+    <t>Mrs. Renuka Rao Joopelli,</t>
+  </si>
+  <si>
+    <t>Mrs. Lavanya Gajjala</t>
+  </si>
+  <si>
+    <t>Mrs. Srujana Alle,</t>
+  </si>
+  <si>
+    <t>Mr. Srinivasa Rao Myneni,</t>
+  </si>
+  <si>
+    <t>Mrs. Kavitha Guduru</t>
+  </si>
+  <si>
+    <t>Mrs. Aagya Mathur,</t>
+  </si>
+  <si>
+    <t>Guru Kripa Design Studio Private Limited - MSME Small</t>
+  </si>
+  <si>
+    <t>S K Seth Jewellers</t>
+  </si>
+  <si>
+    <t>AAECK7089G</t>
+  </si>
+  <si>
+    <t>AAGCH4557C</t>
+  </si>
+  <si>
+    <t>AAJCG9820E</t>
+  </si>
+  <si>
+    <t>AACFS2877H</t>
+  </si>
+  <si>
+    <t>US DL No. 29343335</t>
+  </si>
+  <si>
+    <t>USDL No: 25285694</t>
+  </si>
+  <si>
+    <t>US DL NO. A60887866</t>
+  </si>
+  <si>
+    <t>US DL NO. K36073669224</t>
+  </si>
+  <si>
+    <t>US DL NO. 46741808</t>
+  </si>
+  <si>
+    <t>USDL No: S64616170</t>
+  </si>
+  <si>
+    <t>USDL - S30740174</t>
+  </si>
+  <si>
+    <t>US DL NO. 14383883</t>
+  </si>
+  <si>
+    <t>AUS DL NO. 042561333</t>
+  </si>
+  <si>
+    <t>US DL NO. 948265618</t>
+  </si>
+  <si>
+    <t>DL No. 46474713</t>
+  </si>
+  <si>
+    <t>US DL NO. B65370662</t>
+  </si>
+  <si>
+    <t>USDL No: T61786432</t>
   </si>
   <si>
     <t>['MISSING_PAN_ABOVE_2L']</t>
   </si>
   <si>
+    <t>['MISSING_ADDRESS_PROOF_ABOVE_50K']</t>
+  </si>
+  <si>
     <t>['No valid PAN found in PAN or PAN1 columns']</t>
+  </si>
+  <si>
+    <t>['Address proof missing in both address proof columns']</t>
   </si>
 </sst>
 </file>
@@ -396,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -436,28 +643,626 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2">
+        <v>669500</v>
+      </c>
+      <c r="H2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3">
+        <v>1022000</v>
+      </c>
+      <c r="H3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>1542000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>18790000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6">
+        <v>13683611</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>250000</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7">
+        <v>475000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>307</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8">
+        <v>1065000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>310</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9">
+        <v>570000</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>358</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="K2" t="s">
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10">
+        <v>1255000</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>366</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11">
+        <v>564999.98</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>527</v>
+      </c>
+      <c r="B12" t="s">
         <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12">
+        <v>2240000</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>701</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13">
+        <v>937000</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>745</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14">
+        <v>545000</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>747</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15">
+        <v>984999.99</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>852</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <v>38547472</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>853</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17">
+        <v>15472753</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>1011</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18">
+        <v>865000</v>
+      </c>
+      <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>1047</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19">
+        <v>400000</v>
+      </c>
+      <c r="H19" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>1107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20">
+        <v>1537792</v>
+      </c>
+      <c r="F20" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>1167</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21">
+        <v>5577000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>1168</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22">
+        <v>56788</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23">
+        <v>1169</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23">
+        <v>54783</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
+        <v>1173</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24">
+        <v>1474129</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25">
+        <v>1174</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25">
+        <v>9295000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
